--- a/data/internship_outreach.xlsx
+++ b/data/internship_outreach.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16840" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Companies" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,14 +17,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Outreach'!$A$1:$T$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Settings'!$A$1:$B$1</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,9 +33,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -48,7 +57,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -61,17 +70,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -435,35 +447,21 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AA11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="4" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="35" customWidth="1" min="10" max="10"/>
     <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="12" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="16" max="23"/>
     <col width="50" customWidth="1" min="24" max="24"/>
-    <col width="18" customWidth="1" min="25" max="25"/>
-    <col width="18" customWidth="1" min="26" max="26"/>
-    <col width="18" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="25" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -629,28 +627,65 @@
           <t>Nairobi</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Technology organisation (mock summary).</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Technology and data teams (mock summary).</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Mock evidence -- not a real finding.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://www.safaricom.co.ke/careers</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Data Analyst Intern; Software Intern</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R2" t="n">
+        <v>17</v>
+      </c>
+      <c r="S2" t="n">
+        <v>9</v>
+      </c>
+      <c r="T2" t="n">
+        <v>8</v>
+      </c>
+      <c r="U2" t="n">
+        <v>9</v>
+      </c>
+      <c r="V2" t="n">
+        <v>83</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[MOCK RESULT -- not a real assessment] Retrieved pages mention technology and hiring signals (9 indicators matched).</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>QUALIFY</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -690,28 +725,65 @@
           <t>Nairobi</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>10</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>9</v>
+      </c>
+      <c r="V3" t="n">
+        <v>44</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[MOCK RESULT -- not a real assessment] No evidence could be retrieved, so no confident judgement is possible. This is a data gap, not a negative finding.</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NEEDS_REVIEW</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -751,25 +823,6 @@
           <t>Nairobi</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -812,25 +865,6 @@
           <t>Nairobi</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -873,25 +907,6 @@
           <t>Nairobi</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -934,25 +949,6 @@
           <t>Nairobi</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -995,25 +991,6 @@
           <t>Nairobi</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -1056,25 +1033,6 @@
           <t>Nairobi</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -1117,25 +1075,6 @@
           <t>Nairobi</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -1178,25 +1117,6 @@
           <t>Nairobi</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -1226,14 +1146,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="4" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
@@ -1317,25 +1234,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:T1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="1" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="5" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="9" max="17"/>
     <col width="40" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
@@ -1456,7 +1362,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
@@ -1528,9 +1434,9 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>FILL_IN</t>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>monicawughanga@gmail.com</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1448,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FILL_IN</t>
+          <t>https://www.linkedin.com/in/monica-masae/</t>
         </is>
       </c>
     </row>
@@ -1552,9 +1458,9 @@
           <t>GitHub</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>FILL_IN</t>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/M0nicah</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1496,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FILL_IN</t>
+          <t>Immiediately</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1520,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FILL_IN</t>
+          <t>Nairobi</t>
         </is>
       </c>
     </row>
@@ -1644,6 +1550,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:B1"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/internship_outreach.xlsx
+++ b/data/internship_outreach.xlsx
@@ -629,17 +629,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Technology organisation (mock summary).</t>
+          <t>Safaricom PLC provides telecommunications, mobile money (M-PESA), internet, and digital services in Kenya.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Technology and data teams (mock summary).</t>
+          <t>Extensive telecommunications network infrastructure, mobile financial platforms (M-PESA), cloud solutions, and software development teams.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Mock evidence -- not a real finding.</t>
+          <t>The careers page explicitly features an 'Internship Program' and references software engineers on staff.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -649,38 +649,38 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Data Analyst Intern; Software Intern</t>
+          <t>Data Analyst; Data Science Intern; Data/Research Assistant; Business Intelligence; Data Operations; Software/Web Development</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="R2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V2" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>[MOCK RESULT -- not a real assessment] Retrieved pages mention technology and hiring signals (9 indicators matched).</t>
+          <t>Safaricom PLC is a major telecommunications and digital services provider in Nairobi with an explicit Internship Program listed on its careers portal and a strong technical function including software engineering and digital services.</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -742,16 +742,16 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>https://equitygroupholdings.com/careers</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Data Analyst; Data Science Intern; Business Intelligence; IT; Software/Web Development</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q3" t="n">
         <v>5</v>
@@ -760,25 +760,25 @@
         <v>10</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V3" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>NEEDS_REVIEW</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>[MOCK RESULT -- not a real assessment] No evidence could be retrieved, so no confident judgement is possible. This is a data gap, not a negative finding.</t>
+          <t>The website requests to equitygroupholdings.com and its careers page were unsuccessful due to Incapsula security blocks, preventing verification of current technology functions and contact routes. However, as a major bank based in Nairobi, it likely has IT and data operations, making it a candidate for review once access is resolved.</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://twiga.com</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -823,9 +823,65 @@
           <t>Nairobi</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>10</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>10</v>
+      </c>
+      <c r="V4" t="n">
+        <v>35</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>No evidence retrieved or website recorded for this company, preventing any assessment of its technology function or contactability.</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NEEDS_REVIEW</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -865,9 +921,65 @@
           <t>Nairobi</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Software/Web Development</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>10</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>10</v>
+      </c>
+      <c r="V5" t="n">
+        <v>35</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>The website access was blocked with an HTTP 403 error, resulting in no retrieved evidence. Per instructions, absence of evidence due to a blocked website requires a NEEDS_REVIEW response rather than a rejection, though the current score reflects the lack of verifiable data.</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NEEDS_REVIEW</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -907,9 +1019,65 @@
           <t>Nairobi</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Data Science Intern; Data Analyst; Software/Web Development</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>10</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>35</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>The evidence block states that access to the website was blocked by the website with an HTTP 403 error, resulting in no retrieved text or evidence about the organisation. Therefore, a confident decision cannot be made based on the provided evidence.</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NEEDS_REVIEW</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -936,7 +1104,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://ilabafrica.ac.ke</t>
+          <t>https://ilabafrica.strathmore.edu</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -949,9 +1117,65 @@
           <t>Nairobi</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Strathmore University iLabAfrica is a research and innovation centre focusing on ICT development, artificial intelligence, and digital transformation.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Research, software development, data science, cybersecurity, and IoT projects.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Data Science Intern; Data Analyst; Data/Research Assistant; Software/Web Development Intern</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>15</v>
+      </c>
+      <c r="R7" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="n">
+        <v>8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>10</v>
+      </c>
+      <c r="V7" t="n">
+        <v>88</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Strathmore University iLabAfrica is a dedicated research and innovation centre focusing on ICT, data science, artificial intelligence, and software development, providing an exceptional match for a BSc Data Science student based in Nairobi. While no explicit careers page was found in the text, the organisation hosts specific academic programmes, data science units, and technology research projects that align directly with the student's skills.</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>QUALIFY</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -991,9 +1215,65 @@
           <t>Nairobi</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>No evidence was retrieved because the website could not be connected. As a result, the technical function, maturity, and contactability could not be checked based on the provided data.</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NEEDS_REVIEW</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1033,9 +1313,65 @@
           <t>Nairobi</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>The decision rests on the name alone, as Jamii Cyber Cafe indicates a type of business focused on retail internet and typing services rather than professional technology, data, or software engineering functions.</t>
+        </is>
+      </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1075,9 +1411,65 @@
           <t>Nairobi</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>The decision rests on the name alone, as 'Kilimani Computer Repairs' clearly and unambiguously identifies the business type as a computer repair shop rather than a professional software, data, or technology organisation suited for a BSc Data Science student.</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1117,9 +1509,65 @@
           <t>Nairobi</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>The decision rests on the organisation's name alone, which clearly and unambiguously identifies it as a phone accessories retailer rather than a professional technology or data science organisation.</t>
+        </is>
+      </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">

--- a/data/internship_outreach.xlsx
+++ b/data/internship_outreach.xlsx
@@ -1593,7 +1593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="2"/>
@@ -1666,6 +1666,316 @@
       <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Contact Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Safaricom PLC</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://www.safaricom.co.ke/careers</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>This is the official careers portal of Safaricom PLC intended for job and internship applications. (source: https://www.safaricom.co.ke/careers)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Safaricom PLC</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>advantage@safaricom.co.ke</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://www.safaricom.co.ke/careers</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>This address represents a product or service offering published on the careers page rather than a recruitment or HR inbox. (source: https://www.safaricom.co.ke/careers)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Safaricom PLC</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>customercare@safaricom.co.ke</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://www.safaricom.co.ke/careers</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>This is a customer support email address published on the careers page, which is not handled by hiring teams. (source: https://www.safaricom.co.ke/careers)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>C002</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Equity Bank Kenya</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://equitygroupholdings.com/careers</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>This route is the official careers portal published on the organisation's website. (source: https://equitygroupholdings.com/careers)</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C006</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Strathmore University iLabAfrica</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ilabafrica@strathmore.edu</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://ilabafrica.strathmore.edu/</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>This is a general institutional and contact email address published on the homepage of Strathmore University iLabAfrica. (source: https://ilabafrica.strathmore.edu/)</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
     </row>

--- a/data/internship_outreach.xlsx
+++ b/data/internship_outreach.xlsx
@@ -1991,7 +1991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="3"/>
@@ -2106,6 +2106,248 @@
           <t>Notes</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>O001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Safaricom PLC</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Campaign 2 - Software / Technology Internship</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - software and web development support</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Dear Safaricom PLC Team,
+I am Monica Wughanga Masae, a BSc Data Science student at the Open University of Kenya, graduating in 2027.
+I am writing to enquire about internship or industrial attachment opportunities relating to your software development teams and digital services.
+Through my studies and software projects, I have worked with Python, R, SQL, and web development. I can contribute to application support, data analysis, and technical documentation while building my practical skills in a professional environment.
+I would like to know if you currently consider students for an internship or industrial attachment placement, and who I should direct my application to if not the recipient of this email.
+Thank you for your time.
+Kind regards,
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>O002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C002</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Equity Bank Kenya</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Campaign 4 - General Technology Internship</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - data and technology support</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Dear Equity Bank Kenya Team,
+I am a student at the Open University of Kenya pursuing a BSc in Data Science, with an expected graduation year of 2027.
+I am writing to enquire about opportunities for an internship or industrial attachment involving data, IT, and general technology work.
+Through my studies and personal projects, I have built practical skills in Python, R, SQL, Excel, data analysis, visualization, and basic machine learning, alongside web development and technical reporting. I am looking to contribute these capabilities to your technical operations while gaining hands-on experience in a professional environment.
+Could you please let me know if you would consider an intern or industrial attachment placement, and if so, who the appropriate person is to speak with regarding this?
+Thank you for your time.
+Kind regards,
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>O003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C006</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Strathmore University iLabAfrica</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Campaign 3 - AI / ML Internship</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - AI, ML and data science</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Dear Strathmore University iLabAfrica Team,
+I am a BSc Data Science student at the Open University of Kenya, graduating in 2027.
+I am writing to enquire about internship or industrial attachment opportunities at Strathmore University iLabAfrica, given your focus on ICT development, artificial intelligence, and digital transformation, as well as your work on research, software development, data science, cybersecurity, and IoT projects.
+Through my coursework, I have built skills in Python, R, SQL, data analysis, visualization, and basic machine learning, alongside experience in software projects and technical documentation. I am available immediately for an internship or industrial attachment placement in Nairobi, and I am eager to contribute to your data and technology operations while building on my foundational machine learning knowledge.
+Please let me know if you consider interns or industrial attachment students, and who I should direct my application to if you are the wrong contact.
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>

--- a/data/internship_outreach.xlsx
+++ b/data/internship_outreach.xlsx
@@ -2174,19 +2174,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2255,19 +2247,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2322,12 +2306,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>DRAFTED</t>
+          <t>SENT</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2335,19 +2319,26 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Sent manually via Gmail Sent manually before approval; recorded with --force.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>

--- a/data/internship_outreach.xlsx
+++ b/data/internship_outreach.xlsx
@@ -2174,6 +2174,7 @@
           <t>2026-09-14</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
@@ -2247,6 +2248,7 @@
           <t>2026-09-14</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>NO_REPLY</t>

--- a/data/internship_outreach.xlsx
+++ b/data/internship_outreach.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16840" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16840" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Companies" sheetId="1" state="visible" r:id="rId1"/>
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA11"/>
+  <dimension ref="A1:AA44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1581,6 +1581,3410 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>C011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KCB Group</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://kcbgroup.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>KCB Group is a non-operating holding company that oversees banking and financial services across East Africa.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Financial technology systems, digital banking operations, and regional IT infrastructure supporting banking services.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Mentorship programs and digital and technical skills training are offered as part of career development.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://kcbgroup.com/careers</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Data Analyst Intern; Data Science Intern; Business Intelligence Intern; Technology/IT Intern; Software Development Intern</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>18</v>
+      </c>
+      <c r="R12" t="n">
+        <v>16</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="n">
+        <v>8</v>
+      </c>
+      <c r="U12" t="n">
+        <v>10</v>
+      </c>
+      <c r="V12" t="n">
+        <v>80</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>KCB Group is a major regional financial institution with established operations in Nairobi, offering career development opportunities that mention digital and technical skills training. The evidence explicitly mentions a careers page and a commitment to nurturing talent, aligning well with a data science and technology student.</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>C012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Co-operative Bank of Kenya</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://co-opbank.co.ke</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Provides banking and financial services to personal, business, corporate, and institutional clients in Kenya.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Internet banking systems, digital platforms, and corporate IT operations.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>The careers page lists links to view latest Co-op Bank jobs.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://www.co-opbank.co.ke/careers/</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Business Intelligence Analyst; IT Support; Software Development Intern</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>15</v>
+      </c>
+      <c r="R13" t="n">
+        <v>18</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="n">
+        <v>9</v>
+      </c>
+      <c r="U13" t="n">
+        <v>10</v>
+      </c>
+      <c r="V13" t="n">
+        <v>82</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>The Co-operative Bank of Kenya is a major financial institution with an established digital presence, online banking, and a dedicated careers page linking to job openings. Its large-scale operations support IT, data, and software functions suitable for a data science student based in Nairobi.</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>C013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Absa Bank Kenya</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://absabank.co.ke</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Absa Bank Kenya PLC provides personal, business, corporate, and investment banking services.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Online and mobile banking platforms, digital financial services, and secure internet banking systems.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Grad programmes, internships, bursaries portal listed on the corporate careers pages.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://www.absa.africa/careers/</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Business Intelligence; Data Operations; Software/Web Development; Application Support</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>22</v>
+      </c>
+      <c r="R14" t="n">
+        <v>17</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="n">
+        <v>9</v>
+      </c>
+      <c r="U14" t="n">
+        <v>10</v>
+      </c>
+      <c r="V14" t="n">
+        <v>88</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Absa Bank Kenya operates extensive banking and financial platforms with online banking and app infrastructure, and the corporate careers evidence specifically lists graduate opportunities, internships, and a jobs portal for applicants across Africa including Kenya.</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>C014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NCBA Group</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://ncbagroup.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>NCBA Group is a financial services group offering banking, investment, leasing, and digital business solutions.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>The organisation runs secure internet banking platforms, digital business operations, and transactional portals.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>The careers section invites candidates who are 'starting out or taking your career to the next level' with opportunities to learn and grow.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://ncbagroup.com/careers/</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Business Intelligence Analyst; Data Operations Assistant; IT Support Intern</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>15</v>
+      </c>
+      <c r="R15" t="n">
+        <v>18</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="n">
+        <v>10</v>
+      </c>
+      <c r="U15" t="n">
+        <v>10</v>
+      </c>
+      <c r="V15" t="n">
+        <v>83</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>NCBA Group is a major financial institution with digital business operations and secure online banking platforms based in Nairobi, offering a strong geographic and skill match for data science students. The website features a dedicated careers section with general hiring information, supporting potential entry-level or attachment opportunities.</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>C015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Family Bank Kenya</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://familybank.co.ke</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Family Bank Kenya provides banking, mortgage, loan, and financial services to personal, business, and diaspora customers.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Digital and mobile banking platforms, system integration, enterprise applications support, and software solutions.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://familybank.co.ke/?page_id=2696</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Business Intelligence; Data Operations; Application Support; IT Technology Intern</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>15</v>
+      </c>
+      <c r="R16" t="n">
+        <v>16</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="n">
+        <v>10</v>
+      </c>
+      <c r="U16" t="n">
+        <v>10</v>
+      </c>
+      <c r="V16" t="n">
+        <v>81</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Family Bank Kenya operates an extensive digital and mobile banking platform (PesaPap) and lists professional technology roles such as System Integration Officer, Solution Architect, and Officer Enterprise Applications Support on its careers page. Although explicit internship openings are not detailed in the scraped text, the presence of a robust IT and digital applications function provides strong alignment for a Data Science and technology student based in Nairobi.</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>C016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Britam Holdings</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://britam.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Insurance / Financial services</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Britam Holdings provides insurance, financial, and asset management services across Africa.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Enterprise IT, digital platforms, and data analytics supporting insurance and financial services.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>The website explicitly lists a 'Careers' section with an 'Early Careers' sub-category.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://britam.com/news/britam-foundation-impacts-over-90-000-lives-through-water-health-and-jobs-initiatives</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Data Analyst Intern; Data Science Intern; Business Intelligence Intern; Data Operations Intern; IT / Technology Intern</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>18</v>
+      </c>
+      <c r="R17" t="n">
+        <v>18</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="n">
+        <v>8</v>
+      </c>
+      <c r="U17" t="n">
+        <v>10</v>
+      </c>
+      <c r="V17" t="n">
+        <v>82</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Britam Holdings is a major financial services and insurance enterprise based in Nairobi with a dedicated careers portal featuring 'Early Careers' options. The organization operates large-scale data and business operations that align well with the student's background in Data Science and analytics.</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>C017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>JamboPay</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://jambopay.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fintech / Payments</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>JamboPay provides regulated payment gateway, checkout APIs, and financial transaction infrastructure for merchants, enterprises, and government agencies.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Fintech infrastructure, payment processing APIs, real-time transaction reconciliation, and dashboard reporting systems.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Data/Research Assistant; Business Intelligence; Data Operations; Software/Web Development</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>10</v>
+      </c>
+      <c r="R18" t="n">
+        <v>18</v>
+      </c>
+      <c r="S18" t="n">
+        <v>9</v>
+      </c>
+      <c r="T18" t="n">
+        <v>6</v>
+      </c>
+      <c r="U18" t="n">
+        <v>10</v>
+      </c>
+      <c r="V18" t="n">
+        <v>78</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>JamboPay is a regulated fintech infrastructure company offering APIs, payment gateways, and real-time reconciliation systems in Nairobi, making it an excellent technical fit for a Data Science student. Although no explicit internship programme is mentioned in the evidence, the heavy emphasis on APIs, dashboards, and developer products indicates a robust software and data engineering environment.</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>C018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kopo Kopo</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://kopokopo.co.ke</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fintech / Payments</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Kopo Kopo provides digital payment tools, business cash advances, and merchant services for businesses.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Software development, API services, mobile application maintenance, and digital transaction processing.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>The careers page explicitly notes that there are currently no vacancies available and does not mention a formal internship programme.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://kopokopo.co.ke/careers/</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Business Intelligence; Data Operations; Software/Web Development Intern; Application Support</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>10</v>
+      </c>
+      <c r="R19" t="n">
+        <v>16</v>
+      </c>
+      <c r="S19" t="n">
+        <v>9</v>
+      </c>
+      <c r="T19" t="n">
+        <v>8</v>
+      </c>
+      <c r="U19" t="n">
+        <v>10</v>
+      </c>
+      <c r="V19" t="n">
+        <v>73</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Kopo Kopo provides digital payment tools, cash advances, and mobile applications, indicating strong software and data relevance in Nairobi. The careers page mentions no current vacancies but provides a link to their team and culture, and the company features an API and Developers section.</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>C019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tala Kenya</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://tala.co.ke</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fintech / Lending</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Tala provides mobile-based financial services and credit to millions of customers globally, including Kenya.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Software engineering, cloud engineering, data platform architecture, and analytics operations.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>The careers page lists professional roles and mentions a remote-first setup with an office in Nairobi, though no explicit student internship title is currently named in the sample list.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://tala.co.ke/careers/</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Data/Research Assistant; Business Intelligence; Data Operations; Software/Web Development</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>15</v>
+      </c>
+      <c r="R20" t="n">
+        <v>20</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="n">
+        <v>10</v>
+      </c>
+      <c r="U20" t="n">
+        <v>10</v>
+      </c>
+      <c r="V20" t="n">
+        <v>90</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Tala Kenya is a recognized fintech company that operates an office in Nairobi and explicitly lists engineering, data science, and analytics roles on its careers page. The student's profile in data science, Python, SQL, and analytics matches the technical focus described on the website, and a direct careers page is available for contact.</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>C020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Branch International</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://branch.co.ke</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Fintech / Lending</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Branch International provides instant mobile loans, savings accounts, and bill payment services through a mobile app.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Mobile application development, financial technology infrastructure, and data-driven credit assessment.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>The careers page features links to current openings and mentions working with the Data Science Team and global offices.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://branch.co/ke/careers</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Data Science Intern; Data Analyst; Business Intelligence Intern; Software/Web Development Intern; Data Operations Intern</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>18</v>
+      </c>
+      <c r="R21" t="n">
+        <v>20</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="n">
+        <v>10</v>
+      </c>
+      <c r="U21" t="n">
+        <v>10</v>
+      </c>
+      <c r="V21" t="n">
+        <v>93</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Branch International is a fintech company operating in Nairobi with a dedicated data science team and explicit careers pages, making it an excellent match for a data science student's skills.</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>C021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>M-KOPA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://m-kopa.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fintech / Asset financing</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>M-KOPA is a fintech platform providing digital loans, smartphone financing, and bundled services to everyday earners across multiple African markets.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Fintech platform utilizing digital credit scoring, mobile applications, device protection software, and data analytics to support financial inclusion.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>The careers page explicitly features options to explore open roles, join a talent pool via a profile submission form, and mentions learning and development resources.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://www.m-kopa.com/careers</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Data Science Intern; Data Analyst; Business Intelligence Intern; Data/Research Assistant; Software/Web Development Intern</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>18</v>
+      </c>
+      <c r="R22" t="n">
+        <v>20</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="n">
+        <v>10</v>
+      </c>
+      <c r="U22" t="n">
+        <v>10</v>
+      </c>
+      <c r="V22" t="n">
+        <v>93</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>M-KOPA is a large fintech platform operating in Kenya that uses digital loans, smartphone financing, and data-driven credit assessment, making it highly relevant for a Data Science student. The careers page features open roles, a talent pool submission form, and hybrid/remote working options in Nairobi, providing strong pathways for an attachment or internship.</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>C022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SunCulture</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://sunculture.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Agritech / Hardware + data</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>SunCulture uses off-grid solar technology to provide smallholder farmers with reliable access to water, irrigation, lighting, and mobile charging.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Off-grid solar systems, Pay-As-You-Grow digital platform, and mobile app solutions.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>The company maintains a dedicated careers portal via Freshteam.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://sunculture.freshteam.com/jobs</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Business Intelligence; Data Operations; Software/Web Development Intern</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>15</v>
+      </c>
+      <c r="R23" t="n">
+        <v>16</v>
+      </c>
+      <c r="S23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T23" t="n">
+        <v>8</v>
+      </c>
+      <c r="U23" t="n">
+        <v>10</v>
+      </c>
+      <c r="V23" t="n">
+        <v>75</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>SunCulture develops off-grid solar technology and smart agricultural systems, providing a strong technology environment for data and software roles. Their website lists a careers page hosted on Freshteam, and their business involves data operations, IoT, and digital platforms. The student's background in data science and Python matches well with potential technical operations.</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>C023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Poa Internet</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://poa.co.ke</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Internet service provider</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Data Analyst; IT; Technology</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>10</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>10</v>
+      </c>
+      <c r="V24" t="n">
+        <v>35</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>The evidence retrieval for the website failed because the page had almost no readable text due to being JavaScript-rendered. As a result, there is insufficient evidence to evaluate the organisation's technical functions, internship opportunities, or contact details.</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>C024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Liquid Intelligent Technologies</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://liquid.tech</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Telecom / Cloud infrastructure</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Liquid Intelligent Technologies provides reliable, high-speed connectivity, state-of-the-art data centres, and innovative digital and cloud services across Africa.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Cloud computing, networking, cyber security solutions, data centres, and digital services infrastructure.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>The careers page invites individuals with relevant experience, qualifications, and a passion for telecommunications to email country-specific offices such as kenya.jobs@liquid.tech.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://liquid.tech/careers/</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; IT Support; Software/Web Development; Application Support</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>18</v>
+      </c>
+      <c r="R25" t="n">
+        <v>16</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="n">
+        <v>10</v>
+      </c>
+      <c r="U25" t="n">
+        <v>10</v>
+      </c>
+      <c r="V25" t="n">
+        <v>89</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Liquid Intelligent Technologies provides cloud computing, connectivity, data centres, and cyber security solutions with a designated Kenya office contact email (kenya.jobs@liquid.tech) on their careers page. Their engineering, networking, and IT focus strongly aligns with the student's technology and data background, although specific data science intern listings are not explicitly detailed in the text.</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>C025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Telkom Kenya</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://telkom.co.ke</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Telecommunications</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Telkom Kenya provides telecommunications services, data plans, mobile financial services via T-kash, and business enterprise solutions.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Telecommunications infrastructure, mobile money platforms (T-kash), customer portals, and digital data management.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Graduate program mentioned under the careers page.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://telkom.co.ke/about-us/careers/</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Business Intelligence Analyst; Data Operations; IT / Technology Intern; Software/Web Development Intern</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>20</v>
+      </c>
+      <c r="R26" t="n">
+        <v>18</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="n">
+        <v>8</v>
+      </c>
+      <c r="U26" t="n">
+        <v>10</v>
+      </c>
+      <c r="V26" t="n">
+        <v>86</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Telkom Kenya is a major telecommunications provider offering data, voice, and financial digital services like T-kash, and its careers page explicitly mentions a graduate program indicating potential for student attachment and entry-level roles.</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>C026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Savannah Informatics</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://savannahinformatics.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Healthtech / Health data</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Savannah Informatics delivers connected software solutions, health informatics, and data analytics for healthcare service providers and consumers.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Software engineering, health informatics, data science, and API development for healthcare systems.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>The website explicitly mentions Data Science Fellowships and Internship Opportunities under its careers section.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://www.savannahinformatics.com/careers</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Data Science Intern; Data Analyst; Business Intelligence Intern; Software/Web Development Intern; Data/Research Assistant</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>25</v>
+      </c>
+      <c r="R27" t="n">
+        <v>20</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="n">
+        <v>10</v>
+      </c>
+      <c r="U27" t="n">
+        <v>10</v>
+      </c>
+      <c r="V27" t="n">
+        <v>100</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Savannah Informatics delivers connected software and data solutions for healthcare and explicitly lists Data Science Fellowships and Internship opportunities on its website. The student's background in data science, Python, SQL, and analytics aligns directly with the company's data-driven healthcare informatics work, and contact details and careers pages are readily accessible in Nairobi.</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>C027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Zeraki</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://zeraki.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Edtech / School data analytics</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>5</v>
+      </c>
+      <c r="V28" t="n">
+        <v>7</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>The website content for Zeraki indicates that the domain is currently for sale and shows only a default WordPress placeholder post with no active business or technology operations. There is no evidence of a technology function or internship opportunities.</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>C028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Moringa School</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://moringaschool.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Edtech / Developer training</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Moringa School transforms tech education in Africa by offering market-aligned training courses in software engineering, data science, cybersecurity, and artificial intelligence.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Delivery of technical education, curriculum development, and technical mentorship in software engineering, data science, and AI.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://moringaschool.com/careers/</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Data Science Intern; Data Analyst; Data/Research Assistant; Technical Mentor; Software/Web Development Intern</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>10</v>
+      </c>
+      <c r="R29" t="n">
+        <v>20</v>
+      </c>
+      <c r="S29" t="n">
+        <v>9</v>
+      </c>
+      <c r="T29" t="n">
+        <v>8</v>
+      </c>
+      <c r="U29" t="n">
+        <v>10</v>
+      </c>
+      <c r="V29" t="n">
+        <v>82</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Moringa School is a tech bootcamp and training institution offering programs in data science, software engineering, and AI, aligning well with the student's BSc Data Science background. While the evidence mentions general hiring and technical mentor roles rather than a formal student internship program, the organization's core operations provide a strong technical and data environment.</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>C029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Techno Brain Group</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://techno-brain.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>IT services / Consultancy</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Data Science Intern; Data Analyst; Software/Web Development</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>10</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>5</v>
+      </c>
+      <c r="V30" t="n">
+        <v>40</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>The evidence retrieval failed because the website had almost no readable text due to being JavaScript-rendered. As a result, specific technical functions, contact routes, and internship opportunities could not be verified from the evidence.</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>C030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Seven Seas Technologies</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://seven.co.ke</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>IT services / Systems integration</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Data Science Intern; Data Analyst; Software/Web Development Intern</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>10</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>10</v>
+      </c>
+      <c r="V31" t="n">
+        <v>35</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>No evidence was retrieved because the website page had almost no readable text. Therefore, we cannot verify the organisation's current technical functions, maturity, or contact routes.</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>C031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>University of Nairobi</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://uonbi.ac.ke</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>University / Research</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Data Science Intern; Data/Research Assistant; IT Support</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>10</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>10</v>
+      </c>
+      <c r="V32" t="n">
+        <v>45</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>The evidence retrieval failed due to an SSL certificate error on the website, leaving no verifiable text about the organisation. However, the organisation's name indicates a major university in Nairobi, which typically maintains IT and research functions suitable for data science students, but lack of evidence requires a NEEDS_REVIEW classification.</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>C032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Strathmore University</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://strathmore.edu</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>University / Research</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Data Science Intern; Data Analyst</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>10</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>5</v>
+      </c>
+      <c r="V33" t="n">
+        <v>35</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>The evidence retrieval failed due to an SSL certificate error for https://strathmore.edu, leaving no evidence to assess. Returning NEEDS_REVIEW or REJECT is required when no evidence is available to check.</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>C033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Kenyatta University</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://ku.ac.ke</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>University / Research</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Kenyatta University is a higher education institution offering academic programmes, research, and professional training.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>University IT, digital learning platforms, e-resources, and academic research departments.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>An 'Internship Programme' link is listed in the student menu on the main website.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://www.ku.ac.ke/careers-ku/</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Data/Research Assistant; IT Support</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>18</v>
+      </c>
+      <c r="R34" t="n">
+        <v>18</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="n">
+        <v>9</v>
+      </c>
+      <c r="U34" t="n">
+        <v>10</v>
+      </c>
+      <c r="V34" t="n">
+        <v>83</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Kenyatta University is an established educational institution in Nairobi with an active Careers @ KU page and an Internship Programme link in the student menu, offering relevant academic and technical contexts for a data science student.</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>C034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>JKUAT</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://jkuat.ac.ke</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>University / Engineering and IT</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; IT Support</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>5</v>
+      </c>
+      <c r="R35" t="n">
+        <v>10</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>5</v>
+      </c>
+      <c r="V35" t="n">
+        <v>40</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>The evidence retrieval failed due to an SSL certificate error, leaving no website evidence to check. However, JKUAT is known as a university, which typically has IT and data functions, but the lack of retrievable evidence means manual review is needed.</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>C035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>United States International University Africa</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://usiu.ac.ke</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>University / Research</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>United States International University-Africa is a private university offering undergraduate, master's, and doctoral degree programs in Nairobi.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>An internal IT and digital infrastructure supporting academic systems, e-learning initiatives, and a digital repository.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>The website lists Placement &amp; Career Services, Employer Engagement, and Internships.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://www.usiu.ac.ke/documents/career-fair-2026-information-pack/</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data/Research Assistant; IT Support; Application Support</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>18</v>
+      </c>
+      <c r="R36" t="n">
+        <v>16</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="n">
+        <v>9</v>
+      </c>
+      <c r="U36" t="n">
+        <v>10</v>
+      </c>
+      <c r="V36" t="n">
+        <v>81</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>The evidence shows that United States International University-Africa is a major private university located in Nairobi with internal ITS logins, digital repositories, and career services departments. While it is an academic institution rather than a pure software house, its technology infrastructure and placement opportunities make it a viable host for a data science student.</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Daystar University</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://daystar.ac.ke</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>University / Research</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Daystar University is a higher education institution offering degree, diploma, and certificate programs.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Educational ICT services, e-learning systems, library digital platforms, and administrative technology systems.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>The evidence shows a vacancies section and educational operations, but no specific active student internship program explicitly advertised.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://daystar.ac.ke/vacancies/</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Data Analyst Intern; IT Support Intern; Data/Research Assistant; Application Support</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>15</v>
+      </c>
+      <c r="R37" t="n">
+        <v>16</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="n">
+        <v>8</v>
+      </c>
+      <c r="U37" t="n">
+        <v>10</v>
+      </c>
+      <c r="V37" t="n">
+        <v>77</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Daystar University is an established educational institution operating in Nairobi with academic programs and a Certificate in ICT, providing a plausible environment for a data science and IT attachment. The evidence shows a functioning website with contact and admissions details, and universities commonly host industrial attachments for technology students.</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>C037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>KEMRI</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://kemri.go.ke</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Medical research / Health data</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>The Kenya Medical Research Institute (KEMRI) is a state corporation responsible for carrying out research in human health in Kenya.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Research informatics, biostatistics, data management, and epidemiological analysis via the Department of Epidemiology, Statistics and Informatics (DESI).</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Attachment and Internship Information Sheet and Attachment Portal are explicitly listed on the KEMRI careers page.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://www.kemri.go.ke/careers/</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Data/Research Assistant; Business Intelligence; Data Operations</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>22</v>
+      </c>
+      <c r="R38" t="n">
+        <v>18</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="n">
+        <v>9</v>
+      </c>
+      <c r="U38" t="n">
+        <v>10</v>
+      </c>
+      <c r="V38" t="n">
+        <v>89</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>KEMRI is a large national research corporation in Kenya featuring a dedicated Department of Epidemiology, Statistics and Informatics (DESI) and an explicit attachment portal, making it a strong match for a data science student.</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>C038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>International Livestock Research Institute</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://ilri.org</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Agricultural research / Data science</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Improve food security and reduce poverty through research for better and more sustainable use of livestock.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Data and research methods, datasets, apps, and bioscience platforms.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Capacity development programs and building the next generation of leaders.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://www.ilri.org/index.php/join-us/jobs-careers</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Data/Research Assistant; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>18</v>
+      </c>
+      <c r="R39" t="n">
+        <v>18</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="n">
+        <v>9</v>
+      </c>
+      <c r="U39" t="n">
+        <v>10</v>
+      </c>
+      <c r="V39" t="n">
+        <v>85</v>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>The International Livestock Research Institute features dedicated data and research methods units, datasets, and apps, aligning well with the student's background in data science. Contact details and a careers section are provided with a physical presence in Nairobi, Kenya. Although specific current internship listings are not detailed in the text, the organization actively engages in research capacity development and building the next generation of leaders.</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>C039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CGIAR</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://cgiar.org</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Agricultural research / Data science</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>CGIAR operates as a global agricultural innovation network providing evidence, innovation, and tools to address challenges to food, land, and water systems.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Digital transformation initiatives and a CGIAR AI Hub indicating data, research, and technical operations.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://www.cgiar.org/careers</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Data Science Intern; Data/Research Assistant; Data Analyst; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>15</v>
+      </c>
+      <c r="R40" t="n">
+        <v>18</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="n">
+        <v>8</v>
+      </c>
+      <c r="U40" t="n">
+        <v>10</v>
+      </c>
+      <c r="V40" t="n">
+        <v>81</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>CGIAR is the world's largest global agricultural innovation network, featuring a Digital Transformation area and a CGIAR AI Hub that align well with the student's background in data science. The website provides a Careers link and notes a presence in East and Southern Africa, supporting potential internship opportunities in Nairobi.</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>C040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Deloitte East Africa</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://deloitte.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Professional services / Technology consulting</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Deloitte provides professional services including audit, consulting, financial advisory, risk management, and tax services.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Deloitte operates specialized engineering, artificial intelligence, data analytics, and enterprise technology units.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>The evidence shows dedicated careers pages with job search functionality.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://www.deloitte.com/global/en/careers/job-search.html</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Data Science Intern; Data Analyst; Data/Research Assistant; Business Intelligence Intern; Technology Consulting Intern</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>18</v>
+      </c>
+      <c r="R41" t="n">
+        <v>18</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="n">
+        <v>9</v>
+      </c>
+      <c r="U41" t="n">
+        <v>10</v>
+      </c>
+      <c r="V41" t="n">
+        <v>85</v>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Deloitte East Africa operates major professional services including Engineering, AI &amp; Data, Enterprise Technology &amp; Performance, and IT, Data &amp; Analytics. The evidence shows dedicated career pages and job search portals, aligning well with the student's background in Data Science and technology roles.</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>C041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>KPMG East Africa</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://kpmg.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Professional services / Technology consulting</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>KPMG provides global audit, tax, legal, and advisory services including digital transformation, AI, and technology consulting.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Enterprise technology consulting, digital transformation, AI integration, data analytics, and cloud solutions for clients.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>The careers page explicitly states: 'We welcome people at all levels of their careers, from students and recent graduates to experienced professionals.'</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://kpmg.com/xx/en/careers.html</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Data Analyst Intern; Data Science Intern; Business Intelligence Intern; Technology Consulting Intern; Software/Web Development Intern</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>22</v>
+      </c>
+      <c r="R42" t="n">
+        <v>18</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="n">
+        <v>9</v>
+      </c>
+      <c r="U42" t="n">
+        <v>8</v>
+      </c>
+      <c r="V42" t="n">
+        <v>87</v>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>KPMG is a large global professional services and advisory network with strong technology, digital transformation, and data consulting capabilities, and explicitly welcomes students and recent graduates across its career channels.</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>C042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PwC Kenya</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://pwc.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Professional services / Technology consulting</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Provides professional services including consulting, tax, assurance, and technology solutions.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Consulting, artificial intelligence, data analytics, and digital transformation services.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>University Relations and Student Development Programs including internships are referenced on their careers pages.</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://www.pwc.com/us/en/careers.html</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Business Intelligence Analyst; Technology Consulting Intern</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>18</v>
+      </c>
+      <c r="R43" t="n">
+        <v>17</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="n">
+        <v>8</v>
+      </c>
+      <c r="U43" t="n">
+        <v>8</v>
+      </c>
+      <c r="V43" t="n">
+        <v>81</v>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>PwC Kenya is part of a global professional services network offering consulting, technology, audit, and tax services. The evidence highlights extensive technology, AI, and digital consulting capabilities along with structured student and entry-level career programmes, making it a strong fit for a data science student.</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>Verified list</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>C043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Rudder Research and Data Analytics LTD</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://rudderdatanalytics.co.ke</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Research / Data analytics consultancy</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Research and data analytics consultancy supporting evidence-led decisions for companies, NGOs and SACCOs working in Kenya.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Survey design and field data collection, data cleaning and analysis, dashboards (Power BI, Tableau), reporting.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Actively recruiting: a Data Analyst role (Nairobi, hybrid, KES 60-120k/mo) and Field Enumerator roles were advertised in 2026. Verified from job listings, not from their site (which blocks automated access).</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://ke.linkedin.com/company/rudder-research-and-data-analytics</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Data Analyst; Research Assistant; Data Operations</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>23</v>
+      </c>
+      <c r="R44" t="n">
+        <v>19</v>
+      </c>
+      <c r="S44" t="n">
+        <v>7</v>
+      </c>
+      <c r="T44" t="n">
+        <v>8</v>
+      </c>
+      <c r="U44" t="n">
+        <v>10</v>
+      </c>
+      <c r="V44" t="n">
+        <v>91</v>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Direct match: a Nairobi research and data analytics consultancy whose published services (survey design, data cleaning, Power BI and Tableau dashboards, reporting) map onto the candidate's survey analysis, SQL, Python and BI experience. Actively hiring a Data Analyst. Scored manually from verified job listings and search results; their own website blocks automated access.</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>Applied directly - manually researched</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AA1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1593,7 +4997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="2"/>
@@ -1979,6 +5383,2362 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>C011</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>KCB Group</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://kcbgroup.com/careers</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>This is the official careers portal of KCB Group published on their website. (source: https://kcbgroup.com/careers)</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>C012</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Co-operative Bank of Kenya</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>https://www.co-opbank.co.ke/careers/</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>This is the official careers portal URL published on the organisation's website. (source: https://www.co-opbank.co.ke/careers/)</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>C012</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Co-operative Bank of Kenya</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>customerservice@co-opbank.co.ke</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://www.co-opbank.co.ke/</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>This is a customer service email address published on the main website homepage and is not suitable for handling internship requests. (source: https://www.co-opbank.co.ke/)</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>C013</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Absa Bank Kenya</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>https://www.absa.africa/careers/</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>This is the official careers portal URL published on the organisation's website. (source: https://www.absa.africa/careers/)</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>C014</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NCBA Group</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>https://ncbagroup.com/careers/</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>This is the official careers portal of NCBA Group, which is the primary route for internship and graduate recruitment. (source: https://ncbagroup.com/careers/)</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>C015</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Family Bank Kenya</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>https://familybank.co.ke/?page_id=2696</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>This is the careers portal page for Family Bank Kenya. (source: https://familybank.co.ke/?page_id=2696)</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>C016</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Britam Holdings</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>https://britam.com/news/britam-foundation-impacts-over-90-000-lives-through-water-health-and-jobs-initiatives</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>This route is a careers portal found on the organisation's website. (source: https://britam.com/news/britam-foundation-impacts-over-90-000-lives-through-water-health-and-jobs-initiatives)</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>C018</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Kopo Kopo</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>https://kopokopo.co.ke/careers/</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>This is the dedicated careers portal for Kopo Kopo published on their website. (source: https://kopokopo.co.ke/careers/)</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>C019</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Tala Kenya</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>https://tala.co.ke/careers/</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>This is the official careers portal published on the organisation's website. (source: https://tala.co.ke/careers/)</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>P015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>C020</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Branch International</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://branch.co/ke/careers</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>This is the official careers portal of Branch International, published on their website for job seekers. (source: https://branch.co/ke/careers)</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>C021</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>M-KOPA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>https://www.m-kopa.com/careers</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>This is the official careers portal published on the website. (source: https://www.m-kopa.com/careers)</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>C021</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>M-KOPA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>info@m-kopa.com</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>https://www.m-kopa.com/contact</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>This is a general enquiries address published on the contact page. (source: https://www.m-kopa.com/contact)</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>C022</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SunCulture</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>https://sunculture.freshteam.com/jobs</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>This is the dedicated careers portal hosted on Freshteam for SunCulture job listings. (source: https://sunculture.freshteam.com/jobs)</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>C024</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Liquid Intelligent Technologies</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>botswanahr@liquid.tech</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>https://liquid.tech/careers/</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>This is an HR email address published on the organization's careers page. (source: https://liquid.tech/careers/) WARNING: this address names another country -- check it is the right office before writing.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>C024</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Liquid Intelligent Technologies</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>hr.uganda@liquid.tech</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>https://liquid.tech/careers/</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>This is an HR email address published on the organization's careers page. (source: https://liquid.tech/careers/) WARNING: this address names another country -- check it is the right office before writing.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>P021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>C024</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Liquid Intelligent Technologies</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>hr.zim@liquid.tech</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>https://liquid.tech/careers/</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>This is an HR email address published on the organization's careers page. (source: https://liquid.tech/careers/) WARNING: this address names another country -- check it is the right office before writing.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>P022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>C025</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Telkom Kenya</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>hrenquiries@telkom.co.ke</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>https://telkom.co.ke/help-center/contact-us/</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>This is an HR enquiries email address published on the contact us page. (source: https://telkom.co.ke/help-center/contact-us/)</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>P023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>C025</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Telkom Kenya</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://telkom.co.ke/about-us/careers/</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>This is the dedicated careers portal URL published on the organisation's website. (source: https://telkom.co.ke/about-us/careers/)</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C025</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Telkom Kenya</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>corporatecare@telkom.co.ke</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>https://telkom.co.ke/help-center/contact-us/</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>This is a corporate customer care email address published on the contact us page. (source: https://telkom.co.ke/help-center/contact-us/)</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>P025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Savannah Informatics</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://www.savannahinformatics.com/careers</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>This is the careers portal page for the organisation. (source: https://www.savannahinformatics.com/careers)</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>P026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Savannah Informatics</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>info@savannahinformatics.com</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://www.savannahinformatics.com/</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>This is a general enquiries email address published on the main website. (source: https://www.savannahinformatics.com/)</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>P027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>C028</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Moringa School</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://moringaschool.com/careers/</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>This is the dedicated careers portal for Moringa School published on their website. (source: https://moringaschool.com/careers/)</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>P028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>C033</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Kenyatta University</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://www.ku.ac.ke/careers-ku/</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>This is the official careers portal of the university published on the careers page. (source: https://www.ku.ac.ke/careers-ku/)</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>P029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>C033</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Kenyatta University</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>info@ku.ac.ke</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://www.ku.ac.ke/contact-information/</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>This is a general information email address published on the contact information page. (source: https://www.ku.ac.ke/contact-information/)</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>P030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>C033</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Kenyatta University</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>cfo@ku.ac.ke</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://www.ku.ac.ke/contact-information/</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>This is a finance office email address published on the contact information page. (source: https://www.ku.ac.ke/contact-information/)</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>P031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>C035</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>United States International University Africa</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>careeroffice@usiu.ac.ke</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>https://www.usiu.ac.ke/about-us/contact-us/</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>This is the career office email address published on the contact us page. (source: https://www.usiu.ac.ke/about-us/contact-us/)</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>P032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>C035</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>United States International University Africa</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>https://www.usiu.ac.ke/documents/career-fair-2026-information-pack/</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>This is a careers portal information pack document URL published on the website. (source: https://www.usiu.ac.ke/documents/career-fair-2026-information-pack/)</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>P033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>C035</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>United States International University Africa</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>admit@usiu.ac.ke</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>https://www.usiu.ac.ke/</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>This is the admissions email address published on the main website. (source: https://www.usiu.ac.ke/)</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>P034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>C036</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Daystar University</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>https://daystar.ac.ke/vacancies/</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>This is the careers portal URL published on the organization's website, dedicated to job vacancies and employment opportunities. (source: https://daystar.ac.ke/vacancies/)</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>P035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>C036</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Daystar University</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>admissions@daystar.ac.ke</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>https://daystar.ac.ke/</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>This is an admissions email address published on the main website, which is intended for student enrollment rather than internship inquiries. (source: https://daystar.ac.ke/)</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>P036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>C037</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>KEMRI</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>hr@kemri.go.ke</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>https://www.kemri.go.ke/careers/</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>This is the human resources email address published on the careers page of the organisation's website. (source: https://www.kemri.go.ke/careers/)</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>P037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>C037</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>KEMRI</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://www.kemri.go.ke/careers/</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>This is the official careers portal of the organisation published on their website. (source: https://www.kemri.go.ke/careers/)</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>P038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>C037</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>KEMRI</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>director@kemri.go.ke</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://www.kemri.go.ke/careers/</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>This is the director's office email address published on the careers page and is not a dedicated recruitment channel. (source: https://www.kemri.go.ke/careers/)</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>P039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>C038</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>International Livestock Research Institute</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://www.ilri.org/index.php/join-us/jobs-careers</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>This route is the official careers portal of the organisation, published on the join us and jobs careers page. (source: https://www.ilri.org/index.php/join-us/jobs-careers)</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>P040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>C039</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CGIAR</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>https://www.cgiar.org/careers</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>This route is the official careers portal of the organization published on their website. (source: https://www.cgiar.org/careers)</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>P041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>C040</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Deloitte East Africa</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://www.deloitte.com/global/en/careers/job-search.html</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>This route is the official careers portal for job and internship searches on the organisation's website. (source: https://www.deloitte.com/global/en/careers/job-search.html)</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>P042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>C041</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>KPMG East Africa</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://kpmg.com/xx/en/careers.html</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>This route is the official careers portal of the organisation, which is appropriate for student internship applications. (source: https://kpmg.com/xx/en/careers.html)</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>P043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>C042</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>PwC Kenya</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://www.pwc.com/us/en/careers.html</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>This route is the official careers portal published on the organisation's website. (source: https://www.pwc.com/us/en/careers.html)</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1991,7 +7751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="3"/>
@@ -2174,7 +7934,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
@@ -2235,7 +7994,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -2248,7 +8007,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
@@ -2339,6 +8097,1919 @@
       <c r="T4" t="inlineStr">
         <is>
           <t>Sent manually via Gmail Sent manually before approval; recorded with --force.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>O004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>C026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>P025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Savannah Informatics</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Applied outside the system</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Application to Savannah Informatics</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Recorded manually. This application was made outside this system (applied through their careers portal), so the exact text is not stored here.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>SENT</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Logged manually: applied through their careers portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>O005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C011</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>KCB Group</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Campaign 4 - General Technology Internship</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - data, IT, and technology support</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Dear KCB Group Team,
+I am Monica Wughanga Masae, a BSc Data Science student at the Open University of Kenya, with an expected graduation year of 2027.
+I am writing to enquire about internship or industrial attachment opportunities within your technology function, which oversees financial technology systems, digital banking operations, and regional IT infrastructure supporting banking services.
+Through my studies, I have built practical skills in Python, R, SQL, data analysis, visualization, statistics, and basic machine learning, alongside exposure to software projects and web development. I am looking for a placement where I can contribute to data and technology operations while building my technical skills in a professional environment.
+Could you please let me know if you consider interns or industrial attachment students, or direct me to the appropriate person to speak with regarding these opportunities?
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>O006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>C012</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Co-operative Bank of Kenya</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Campaign 2 - Software / Technology Internship</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - software and web development support</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Dear Co-operative Bank of Kenya Team,
+I am a BSc Data Science student at the Open University of Kenya, graduating in 2027. I am writing to enquire about an internship or industrial attachment.
+Co-operative Bank of Kenya provides banking and financial services to personal, business, corporate, and institutional clients in Kenya, and operates internet banking systems, digital platforms, and corporate IT operations.
+Through my studies and personal projects, I have built practical skills in Python, SQL, R, data analysis, web development, and software projects, along with experience in technical documentation and reporting. I am looking to contribute to your digital platforms, software projects, and application support work while developing my technical capabilities further in a professional environment.
+Could you please let me know if you consider interns or industrial attachment students for your technology operations, and who I should direct my application to if there are current opportunities?
+Thank you for your time.
+Kind regards,
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>O007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>C013</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Absa Bank Kenya</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Campaign 2 - Software / Technology Internship</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - software development and application support</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Dear Absa Bank Kenya Team,
+I am a student at the Open University of Kenya pursuing a BSc in Data Science with an expected graduation year of 2027.
+I am writing to enquire about internship or industrial attachment opportunities related to your online and mobile banking platforms, digital financial services, and secure internet banking systems.
+Through my studies and personal software projects, I have built practical skills in Python, SQL, web development, and software applications, and I am keen to support your technical operations while learning from your team.
+Please let me know if you are currently considering interns or industrial attachment students for software development and application support work, or who I should contact regarding these opportunities.
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>O008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>C014</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NCBA Group</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Campaign 2 - Software / Technology Internship</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - software and web development, BSc Data Science student</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Dear NCBA Group Team,
+I am Monica Wughanga Masae, a BSc Data Science student at the Open University of Kenya, graduating in 2027. I am reaching out to enquire about an internship or industrial attachment placement.
+I am interested in your technology function, which runs secure internet banking platforms, digital business operations, and transactional portals.
+Through my studies and personal work, I have built skills in Python, SQL, web development, software projects, and application support. I am looking to contribute to your software and web development or application support work while developing my technical capabilities further.
+Would you consider an intern or industrial attachment placement for these areas, and if not, who would be the correct person to speak to?
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>O009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>C015</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Family Bank Kenya</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Campaign 2 - Software / Technology Internship</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - software and web development</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Dear Family Bank Kenya Team,
+I am Monica Wughanga Masae, a BSc Data Science student at the Open University of Kenya with an expected graduation year of 2027.
+I am writing to express my interest in an internship or industrial attachment focusing on software and web development, and application support work, aligned with your technology function supporting digital and mobile banking platforms, system integration, and enterprise applications.
+Through my studies and personal software projects, I have built practical skills in Python, SQL, web development, and technical documentation. I am eager to apply my technical foundation, contribute to your application support and development efforts, and learn how banking and financial technology systems operate in practice.
+Could you please let me know if you would consider an intern or industrial attachment placement for these areas, and who the appropriate person to speak with would be if this falls outside your team?
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>O010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>C016</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Britam Holdings</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Campaign 1 - Data / Analytics Internship</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Internship enquiry - data analysis and reporting, BSc Data Science student</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Dear Britam Holdings Team,
+I am a BSc Data Science student at the Open University of Kenya, graduating in 2027.
+I am reaching out regarding internship and industrial attachment opportunities to support your data analytics, enterprise IT, and digital platform functions.
+Through my studies and personal projects, I have built practical skills in Python, R, SQL, Excel, data analysis, and data visualization using Tableau. I am looking to contribute to your reporting and data analysis work while further developing my technical skills.
+Could you please let me know if you consider interns or industrial attachment students for these teams, and who the appropriate person is to speak with regarding placement?
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>O011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>C018</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Kopo Kopo</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Campaign 2 - Software / Technology Internship</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - software and web development</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Dear Kopo Kopo Team,
+I am a BSc Data Science student at the Open University of Kenya, graduating in 2027.
+I am writing to enquire about potential internship or industrial attachment opportunities in software and web development, and application support work, given that Kopo Kopo provides digital payment tools, business cash advances, and merchant services, with a technology function covering software development, API services, mobile application maintenance, and digital transaction processing.
+Through my studies and personal projects, I have built practical skills in Python, SQL, web development, software projects, and application support. I am eager to apply these foundational skills to support your technology operations while learning from your team.
+Could you please let me know if you would consider an intern or industrial attachment placement, and who I might speak with if this is handled elsewhere?
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>O012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>C019</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>P014</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Tala Kenya</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Campaign 1 - Data / Analytics Internship</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Internship enquiry - data analysis and reporting, BSc Data Science student</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Dear Tala Kenya Team,
+I am Monica Wughanga Masae, a BSc Data Science student at the Open University of Kenya, graduating in 2027.
+I am writing to ask about opportunities for an internship or industrial attachment, specifically regarding data analysis, reporting, and visualisation work.
+Through my studies and software projects, I work with Python, R, SQL, and Excel, and I have exposure to Tableau. I want to apply these skills to support analytics operations while building practical experience.
+Could you please let me know if you take on interns or industrial attachment students, and who the appropriate person to contact would be if not you?
+Thank you for your time.
+Kind regards,
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>O013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>C020</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>P015</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Branch International</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Campaign 1 - Data / Analytics Internship</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - data analysis, reporting and visualisation</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Dear Branch International Team,
+I am Monica Wughanga Masae, studying for a BSc in Data Science at the Open University of Kenya, with an expected graduation in 2027. I am seeking an internship or industrial attachment based in Nairobi.
+I note that you provide instant mobile loans, savings accounts, and bill payment services through a mobile app, and that your careers page mentions working with the Data Science Team.
+Through my studies and software projects, I have built practical skills in Python, R, SQL, data analysis, reporting, and data visualization, including exposure to Tableau. I want to contribute to your data analysis, reporting, and visualisation work while building my professional skills.
+I would like to know if you currently consider students for internship or industrial attachment placements. If you are not the right person to speak to regarding this, could you direct me to the appropriate team?
+Thank you for your time.
+Kind regards,
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>O014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>C021</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>P016</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>M-KOPA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Campaign 1 - Data / Analytics Internship</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - data analysis and reporting, BSc Data Science student</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Dear M-KOPA Team,
+My name is Monica Wughanga Masae, and I am studying for a BSc in Data Science at the Open University of Kenya, with an expected graduation in 2027.
+I am reaching out regarding internship and industrial attachment opportunities because of your work as a fintech platform providing digital loans, smartphone financing, and bundled services, which utilizes digital credit scoring, mobile applications, device protection software, and data analytics.
+Through my coursework and projects, I have built practical skills in Python, R, SQL, and Excel, with a strong focus on data analysis, reporting, and visualization using Tableau. I am eager to contribute to your data operations and reporting work while continuing to develop my technical capabilities.
+I would like to ask if you would consider an intern or industrial attachment placement for this type of work, and who I should speak to if you are not the correct contact.
+Thank you for your time.
+Kind regards,
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>O015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>C022</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>P018</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SunCulture</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Campaign 2 - Software / Technology Internship</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - software and web development</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Dear SunCulture Team,
+I am a student pursuing a BSc Data Science at the Open University of Kenya, with an expected graduation year of 2027.
+I am writing to enquire about internship or industrial attachment opportunities relating to your software and web development and application support work, which includes your off-grid solar systems, Pay-As-You-Grow digital platform, and mobile app solutions.
+Through my studies and personal projects, I have built skills in Python, SQL, web development, and software projects, along with technical documentation and basic machine learning. I am looking for a placement in Nairobi where I can contribute to your technical operations while building practical experience.
+Could you please let me know if you would consider an intern or industrial attachment placement, and who I should direct this query to if applications are handled elsewhere?
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>O016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>C024</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>P019</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Liquid Intelligent Technologies</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Campaign 2 - Software / Technology Internship</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - software and web development support</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Dear Liquid Intelligent Technologies Team,
+I am a BSc Data Science student at the Open University of Kenya, graduating in 2027.
+I note that you provide reliable, high-speed connectivity, state-of-the-art data centres, and innovative digital and cloud services across Africa, with a technology function focused on cloud computing, networking, cyber security solutions, data centres, and digital services infrastructure.
+Through my studies and personal projects, I have built practical skills in Python, SQL, web development, and software projects, along with data analysis and reporting. I am looking for an internship or industrial attachment to contribute to software and web development or application support work while developing my technical capabilities.
+Could you please let me know if you would consider an intern or industrial attachment placement, and who I should speak with if you are not the correct contact?
+Kind regards,
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>O017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>C025</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>P022</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Telkom Kenya</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Campaign 2 - Software / Technology Internship</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - software and web development</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Dear Telkom Kenya Team,
+I am a student at the Open University of Kenya studying for a BSc in Data Science, with an expected graduation year of 2027.
+I am contacting you because Telkom Kenya provides telecommunications services, data plans, mobile financial services via T-kash, and business enterprise solutions.
+Through my coursework and personal projects, I have worked with Python, SQL, R, web development, and software projects, along with basic machine learning and data analysis. I am looking for an internship or industrial attachment to build on these skills through practical work in software and web development, and application support.
+I would like to know if you would consider an intern or industrial attachment placement for these areas. If you are not the correct person to speak to regarding this, could you direct me to the appropriate team?
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>SENT</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gmail message id: 1a0a04f1844a568e</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>O018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>C026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>P025</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Savannah Informatics</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Campaign 1 - Data / Analytics Internship</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Internship enquiry - data analysis and reporting, BSc Data Science student</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Dear Savannah Informatics Team,
+I am Monica Wughanga Masae, a BSc Data Science student at the Open University of Kenya graduating in 2027.
+I note that Savannah Informatics delivers connected software solutions, health informatics, and data analytics for healthcare service providers and consumers, and that your careers section mentions data science fellowships and internship opportunities.
+I am seeking an internship or industrial attachment where I can contribute my skills in data analysis, reporting, visualisation, Python, R, and SQL, while building on my foundational work in software projects and technical documentation. I am available immediately in Nairobi to support your data and technology operations as an early-career learner.
+Could you please let me know if you would consider an intern or industrial attachment placement, and who the appropriate person is to speak with if this falls outside your current scope?
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>O019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>C028</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>P027</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Moringa School</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Campaign 3 - AI / ML Internship</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Internship enquiry - AI, machine learning and data science, BSc Data Science student</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Dear Moringa School Team,
+I am a BSc Data Science student at the Open University of Kenya, graduating in 2027.
+I am writing to enquire about internship or industrial attachment opportunities because of your focus on technical education, curriculum development, and technical mentorship in software engineering, data science, and artificial intelligence.
+Through my coursework and software projects, I have built skills in Python, R, SQL, data analysis, data visualization, and basic machine learning, along with an interest in AI-powered applications. I am looking to contribute to your technical or data operations while developing practical industry experience.
+Could you please let me know if you consider interns or industrial attachment students, and who I should direct my application to if there is an appropriate contact?
+Thank you for your time.
+Kind regards,
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>O020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>C033</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>P028</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Kenyatta University</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Campaign 2 - Software / Technology Internship</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - software and web development support</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Dear Kenyatta University Team,
+I am a BSc Data Science student at the Open University of Kenya, expecting to graduate in 2027.
+I am writing to enquire about opportunities within your university IT, digital learning platforms, e-resources, and academic research departments, noting your listed Internship Programme.
+Through my studies, I have built skills in Python, R, SQL, Excel, and web development, along with software projects, technical documentation, and application support. I am eager to apply these capabilities to software and web development work and to learn from your team.
+Could you please consider me for an internship or industrial attachment placement, or direct me to the appropriate person to speak with if this is not the right contact?
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>O021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>C035</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>P031</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>United States International University Africa</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Campaign 4 - General Technology Internship</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - data, IT and technology support</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Dear United States International University Africa Team,
+I am a student at the Open University of Kenya pursuing a BSc in Data Science, with an expected graduation year of 2027.
+I am writing to enquire about internship or industrial attachment opportunities within your technology function, which supports academic systems, e-learning initiatives, and a digital repository.
+Through my studies and personal projects, I have built practical skills in Python, R, SQL, data analysis, and basic software development. I am eager to apply these skills to support data, IT, and general technology work while learning from your team.
+Please let me know if you would consider an intern or industrial attachment placement, and who I should speak to if this falls outside your remit.
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>SENT</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gmail message id: 1a0a04f90530245d</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>O022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>C036</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>P034</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Daystar University</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Campaign 2 - Software / Technology Internship</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - software and web development support</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Dear Daystar University Team,
+I am Monica Wughanga Masae, a BSc Data Science student at the Open University of Kenya, with an expected graduation year of 2027.
+I am writing to enquire about internship or industrial attachment opportunities at Daystar University, particularly regarding your educational ICT services, e-learning systems, library digital platforms, and administrative technology systems.
+Through my studies and software projects, I have built skills in Python, R, SQL, web development, software projects, and application support. I am capable and willing to work, and I want to contribute to your technology operations while gaining practical experience.
+Would you consider taking on an intern or industrial attachment student for software and web development or application support work? If you do not handle these placements, please let me know who I should contact.
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>O023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>C037</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>P036</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>KEMRI</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Campaign 1 - Data / Analytics Internship</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - data analysis, reporting and visualisation</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Dear KEMRI Team,
+I am a BSc Data Science student at the Open University of Kenya, graduating in 2027. I am writing to enquire about an internship or industrial attachment placement.
+KEMRI is a state corporation responsible for carrying out research in human health in Kenya, with a technology function covering research informatics, biostatistics, data management, and epidemiological analysis via the Department of Epidemiology, Statistics and Informatics.
+Through my studies and software projects, I have built practical skills in data analysis, reporting, data visualization, Python, R, and SQL. I am looking to apply these skills to support data management and analysis tasks while gaining practical experience in a research environment.
+Could you please let me know if you are currently considering interns or industrial attachment students, and who the appropriate person to speak with would be if not you?
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>O024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C038</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>P039</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>International Livestock Research Institute</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Campaign 2 - Software / Technology Internship</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - software and web development support</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Dear International Livestock Research Institute Team,
+I am Monica Wughanga Masae, a BSc Data Science student at the Open University of Kenya, graduating in 2027.
+I am writing to enquire about internship or industrial attachment opportunities. Your work involves research for better and more sustainable use of livestock to improve food security and reduce poverty, utilizing data and research methods, datasets, apps, and bioscience platforms.
+Through my studies and personal projects, I have built skills in software and web development, application support, Python, SQL, data analysis, and technical documentation. I am eager to contribute to your technology function while learning practical workflows.
+Could you please let me know if you consider interns or industrial attachment students for software, web development, or application support work, and who I should direct my application to if not yourselves?
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>O025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C039</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>P040</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CGIAR</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Campaign 4 - General Technology Internship</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - technology, IT and data work</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Dear CGIAR Team,
+I am a BSc Data Science student at the Open University of Kenya, with an expected graduation year of 2027.
+I am writing to express my interest in your work involving digital transformation initiatives and the CGIAR AI Hub, which point to data, research, and technical operations.
+Through my studies and software projects, I have built practical skills in Python, R, SQL, data analysis, visualization, basic machine learning, and web development. I am looking for an internship or industrial attachment to apply these technical foundations and learn from your team.
+Could you please let me know if you would consider an intern or attachment student for technology, IT, or data roles, or direct me to the appropriate person to speak with regarding such opportunities?
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>O026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C040</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>P041</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Deloitte East Africa</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Campaign 3 - AI / ML Internship</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - AI, data analytics and technology, BSc Data Science student</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Dear Deloitte East Africa Team,
+I am a BSc Data Science student at the Open University of Kenya, graduating in 2027. I am contacting you because Deloitte operates specialized engineering, artificial intelligence, data analytics, and enterprise technology units as part of your professional services.
+Through my coursework and software projects, I have built practical skills in Python, R, SQL, data analysis, visualization, and basic machine learning. I am looking to apply these competencies and learn more through an internship or industrial attachment.
+I would like to know if you currently consider students for internship or industrial attachment placements in your technology or data functions. If you are not the correct person to direct this enquiry to, could you please let me know who I should contact?
+Thank you for your time.
+Kind regards,
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>O027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>C041</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>P042</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>KPMG East Africa</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Campaign 1 - Data / Analytics Internship</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Internship enquiry - data analysis, BSc Data Science student</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Dear KPMG East Africa Team,
+I am a BSc Data Science student at the Open University of Kenya, expecting to graduate in 2027.
+I am reaching out because KPMG provides digital transformation, AI, and technology consulting services, and notes on its careers page that it welcomes students and recent graduates.
+Through my studies and software projects, I have built skills in data analysis, reporting, data visualization, Python, R, SQL, and Excel. I am looking for an internship or industrial attachment where I can contribute to data analysis and reporting work while continuing to develop my technical capabilities.
+Could you please let me know if you consider students for internships or industrial attachments, and who the appropriate person is to speak with regarding these opportunities?
+Thank you for your time.
+Kind regards,
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>O028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>C042</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>P043</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PwC Kenya</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Campaign 3 - AI / ML Internship</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Internship enquiry - AI, machine learning and data analytics - BSc Data Science student</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Dear PwC Kenya Team,
+I am a BSc Data Science student at the Open University of Kenya, with an expected graduation year of 2027.
+I am writing to enquire about internship or industrial attachment opportunities in your technology function, which provides consulting, artificial intelligence, data analytics, and digital transformation services.
+Through my coursework and software projects, I have built skills in Python, R, SQL, data analysis, visualization, and basic machine learning, along with an interest in AI-powered applications. I am looking to apply these skills and develop my capabilities further in a professional environment.
+Could you please let me know if you consider students for internships or industrial attachments, and who I should direct this enquiry to if applications are handled elsewhere?
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>O029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>C043</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Rudder Research and Data Analytics LTD</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Applied outside the system</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Application to Rudder Research and Data Analytics LTD</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Recorded manually. This application was made outside this system (applied via their website with tailored CV and cover letter), so the exact text is not stored here.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>SENT</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Logged manually: applied via their website with tailored CV and cover letter</t>
         </is>
       </c>
     </row>

--- a/data/internship_outreach.xlsx
+++ b/data/internship_outreach.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16840" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4420" yWindow="660" windowWidth="24980" windowHeight="16840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Companies" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,10 +12,10 @@
     <sheet name="Settings" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$AA$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Contacts'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Outreach'!$A$1:$T$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Settings'!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$AA$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Contacts'!$A$1:$L$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Outreach'!$A$1:$T$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Settings'!$A$1:$B$15</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -446,17 +446,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA44"/>
+  <dimension ref="A1:AA78"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
-    <col width="35" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="13"/>
+    <col width="18" customWidth="1" min="4" max="5"/>
+    <col width="35.5" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="8"/>
+    <col width="134.6640625" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="119.1640625" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="158.33203125" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="89.83203125" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="23"/>
@@ -4985,8 +4988,1606 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>C044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Leta</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://leta.ai</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>AI Logistics Software</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>Search: logistics technology company Nairobi</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>C045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BETA Agriculture Technologies</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.betaagritech.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>AgriTech</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>Search: agritech data company Kenya</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>C046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>AgriKenya</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://agrikenya.co.ke</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Digital Solutions / AgriTech</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>Search: agritech data company Kenya</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>C047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>InsurTech Forum Nairobi</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://insurtechforum.insure</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Fintech / InsurTech</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>Search: insurtech Nairobi Kenya</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>C048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>bolttech</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://bolttech.io</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>InsurTech</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>Search: insurtech Nairobi Kenya</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>C049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>World Food Programme</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://wfp.org</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>UN agency / Humanitarian data</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>C050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>World Health Organization</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://who.int</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>UN agency / Health data</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>C051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>World Bank</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://worldbank.org</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>International finance / Development data</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>C052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Kenya Red Cross Society</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://redcross.or.ke</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Humanitarian / Emergency data systems</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>C053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Amref Health Africa</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://amref.org</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Health NGO / Health informatics</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>C054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PATH</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://path.org</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Global health NGO / Health data</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>C055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Population Services International</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://psi.org</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Global health NGO / M&amp;E</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>C056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CARE International</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://care.org</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Humanitarian NGO / M&amp;E</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>C057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Oxfam</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://oxfam.org</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Humanitarian NGO / Research</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>C058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ActionAid</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://actionaid.org</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Development NGO / M&amp;E</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>C059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Mercy Corps</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://mercycorps.org</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Humanitarian NGO / Data and evidence</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>C060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ICT Authority Kenya</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://icta.go.ke</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Government / National ICT</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>C061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Kenya National Bureau of Statistics</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://knbs.or.ke</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Government / Official statistics</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>C062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Central Bank of Kenya</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://centralbank.go.ke</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Government / Financial data</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>C063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Communications Authority of Kenya</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://cak.go.ke</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Government regulator / Telecom data</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>C064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>National Hospital Insurance Fund</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://nhif.or.ke</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Government / Health insurance systems</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>C065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>The National Treasury Kenya</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://treasury.go.ke</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Government / Public finance data</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>C066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Nairobi City County</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://nairobi.go.ke</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>County government / Public services data</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>C067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Kenya National Highways Authority</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://kenha.co.ke</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Government agency / Infrastructure data</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>C068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>National Industrial Training Authority</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://nita.go.ke</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Government / Training and skills data</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>C069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Kenya Power</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://kplc.co.ke</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Utility / Energy data systems</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>C070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Wasoko</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://wasoko.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>B2B e-commerce startup / Logistics tech</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>C071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Pezesha</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://pezesha.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Fintech startup / Embedded lending</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>C072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>4G Capital</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://4g-capital.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Fintech / Micro-lending data</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>C073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Turaco</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://turaco.insure</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Insurtech startup</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>C074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Jumia Kenya</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://jumia.co.ke</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>E-commerce / Marketplace data</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>C075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Little Cab</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://littlecab.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Ride-hailing / Mobility tech</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>C076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://glovoapp.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Delivery platform / Logistics data</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>C077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Bolt</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://bolt.eu</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Ride-hailing / Mobility data</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>Curated sector list</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA1"/>
+  <autoFilter ref="A1:AA78"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7740,7 +9341,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7751,15 +9352,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T30"/>
+  <dimension ref="A1:T51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="6"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="36.6640625" bestFit="1" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="17"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="12.83203125" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="13.5" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="15.33203125" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="17"/>
     <col width="40" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
@@ -9180,12 +10786,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>DRAFTED</t>
+          <t>NOT_STARTED</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9196,6 +10802,11 @@
       <c r="P19" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Duplicate of O004 - already applied via their careers portal.</t>
         </is>
       </c>
     </row>
@@ -9997,24 +11608,1545 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr">
         <is>
           <t>Logged manually: applied via their website with tailored CV and cover letter</t>
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>O030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>C043</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>P046</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Rudder Research and Data Analytics LTD</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Campaign 1 - Data / Analytics Internship</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Internship enquiry - data analysis and reporting, BSc Data Science student</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Dear Rudder Research and Data Analytics LTD Team,
+My name is Monica Wughanga Masae, and I am studying BSc Data Science at the Open University of Kenya, with an expected graduation in 2027.
+I am reaching out because your consultancy supports evidence-led decisions through research, data cleaning and analysis, dashboards, and reporting for companies, NGOs, and SACCOs working in Kenya.
+I can contribute practical skills in Python, R, SQL, Excel, data analysis, data visualization, and reporting from my studies and software projects. I want to build on these skills through hands-on work with survey design, field data collection, and data analysis.
+I am writing to ask whether you would consider a student for an internship or industrial attachment placement in Nairobi. If you do not currently host interns, please let me know the appropriate person to speak with regarding data analyst roles.
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>NOT_STARTED</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Duplicate of O029 - already applied via their website on 2026-09-14.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>O031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>C048</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>P047</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>bolttech</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Campaign 2 - Software / Technology Internship</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - software and web development support</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Dear bolttech Team,
+I am Monica Wughanga Masae, a BSc Data Science student at the Open University of Kenya graduating in 2027.
+I am writing to enquire about internship or industrial attachment opportunities relating to your work in operating an international insurtech business providing a B2B2C protection and insurance platform, specifically regarding the development and maintenance of digital insurance distribution engines, embedded insurance APIs, data insights platforms, and no-code product configurators.
+Through my studies and personal projects, I have built practical skills in Python, SQL, web development, software projects, and technical documentation, and I am keen to apply and expand these abilities in application support and software development tasks.
+I would like to know if you would consider taking on an intern or industrial attachment student for this type of work, and if not, who the appropriate person to speak with would be.
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>O032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>C049</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>P048</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>World Food Programme</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Campaign 1 - Data / Analytics Internship</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Internship enquiry - data analysis, reporting and visualisation, BSc Data Science student</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Dear World Food Programme Team,
+I am a student at the Open University of Kenya pursuing a BSc in Data Science, with an expected graduation in 2027. I am writing to enquire about an internship or industrial attachment.
+I am interested in your work delivering food assistance and supporting sustainable livelihoods worldwide, specifically regarding your data analysis, reporting, and logistics systems supporting global humanitarian operations.
+Through my studies and personal projects, I have built practical skills in Python, R, SQL, Excel, data analysis, data visualization, and Tableau exposure. I am looking for an opportunity to contribute to data analysis, reporting, and visualisation work while learning from your team.
+I am available immediately in Nairobi and would like to know if you consider interns or industrial attachment students. If you are not the correct person to speak with regarding this, could you please direct me to the appropriate contact.
+Thank you for your time.
+Kind regards,
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>O033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>C050</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>P049</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>World Health Organization</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Campaign 1 - Data / Analytics Internship</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Internship enquiry - data analysis, BSc Data Science student</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Dear World Health Organization Team,
+My name is Monica Wughanga Masae, and I am studying for a BSc in Data Science at the Open University of Kenya, with an expected graduation in 2027.
+I am reaching out because you maintain extensive global health data and research operations, and handle data collection, global health estimates, statistical dashboards, and health information systems.
+I can contribute skills in data analysis, reporting, visualisation, Python, R, SQL, and Excel through my studies and projects. I want to learn more about applying these methods to public health data operations.
+Could you please consider me for an internship or industrial attachment placement in Nairobi, or let me know who I should speak with regarding such opportunities?
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>O034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>C051</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>P050</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>World Bank</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Campaign 2 - Software / Technology Internship</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - software and web development support</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Dear World Bank Team,
+I am a BSc Data Science student at the Open University of Kenya, graduating in 2027, writing to enquire about an internship or industrial attachment.
+My studies focus on data collection, digital development initiatives, and information technology infrastructure supporting global operations.
+Through my coursework and personal projects, I have worked with Python, SQL, web development, and software projects, along with basic machine learning, data analysis, and reporting. I want to contribute these skills to your software and web development work while building practical experience in application support and technology operations.
+I would like to know if you consider students for internship or industrial attachment placements in this area, and who the appropriate person to contact would be if not you.
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>O035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>C052</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>P051</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Kenya Red Cross Society</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Campaign 4 - General Technology Internship</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - data, IT, and general technology support</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Dear Kenya Red Cross Society Team,
+I am Monica Wughanga Masae, a BSc Data Science student at the Open University of Kenya, graduating in 2027.
+I am reaching out regarding potential opportunities for an internship or industrial attachment to support general technology, IT, and data work within your humanitarian relief operations.
+Through my studies and software projects, I have built practical skills in Python, R, SQL, Excel, data analysis, visualization, and basic machine learning, alongside exposure to Tableau and web development. I am eager to apply these technical abilities and learn from your team.
+Could you please let me know if you consider students for internships or industrial attachments, and who the appropriate person to contact would be if this falls outside your purview?
+Thank you for your time.
+Kind regards,
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>O036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>C053</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>P052</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Amref Health Africa</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Campaign 4 - General Technology Internship</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - technology, IT and data work</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Dear Amref Health Africa Team,
+I am a BSc Data Science student at the Open University of Kenya, with an expected graduation year of 2027.
+I am writing to enquire about potential internship or industrial attachment opportunities related to your technology function, which involves monitoring, evaluation, research publications, and digital health initiatives.
+Through my studies, I have built practical skills in Python, R, SQL, Excel, data analysis, data visualization, basic machine learning, and software projects. I am eager to apply these technical skills to support your data operations and technology work while further developing my capabilities.
+Could you please let me know if you consider students for internships or industrial attachments, and who the appropriate person is to contact regarding such opportunities?
+Thank you for your time.
+Kind regards,
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>O037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>C054</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>P054</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PATH</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Campaign 4 - General Technology Internship</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - technology, IT and data work</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Dear PATH Team,
+I am Monica Wughanga Masae, a BSc Data Science student at the Open University of Kenya with an expected graduation year of 2027.
+I am writing to enquire about internship or industrial attachment opportunities relating to your technology, IT and data work.
+Through my studies and personal projects, I have built practical skills in Python, R, SQL, Excel, data analysis, visualization, basic machine learning, and software projects.
+I am seeking an internship or industrial attachment placement in Nairobi to apply these skills and learn from your team, and I am available to start immediately. If you do not currently host interns or attachments, could you let me know who might be appropriate to speak with regarding these opportunities.
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>O038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>C055</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>P056</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Population Services International</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Campaign 4 - General Technology Internship</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - data analysis and technology, BSc Data Science student</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Dear Population Services International Team,
+I am Monica Wughanga Masae, a BSc Data Science student at the Open University of Kenya, graduating in 2027.
+I am reaching out regarding potential opportunities because your work involves digital health projects and data management across global health initiatives.
+Through my studies and software projects, I have built practical skills in Python, R, SQL, Excel, data analysis, data visualization, basic machine learning, and technical documentation. I am available immediately for an internship or industrial attachment to support your technology function while learning from your team.
+Could you please let me know if you would consider a student placement, and who I might speak with if applications are handled elsewhere?
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>O039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>C056</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>P057</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CARE International</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Campaign 2 - Software / Technology Internship</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - software and web development support</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Dear CARE International Team,
+I am Monica Wughanga Masae, a BSc Data Science student at the Open University of Kenya with an expected graduation year of 2027.
+I am writing to enquire about internship or industrial attachment opportunities. I note from your careers page that you feature a search for internships option, and I am interested in supporting the technology and operational functions involved in your humanitarian aid and development work.
+Through my studies and software projects, I have built skills in Python, SQL, web development, and software applications. I want to contribute to your software and web development or application support tasks while learning how data and technology are applied in an international organisation.
+Could you please let me know if you consider interns or industrial attachments, and who I should direct this enquiry to if you are not the correct contact?
+Kind regards,
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>O040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>C057</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>P059</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Oxfam</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Campaign 4 - General Technology Internship</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - data, IT, and technology support</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Dear Oxfam Team,
+I am a BSc Data Science student at the Open University of Kenya, expecting to graduate in 2027. I am writing to express my interest in joining your organisation for an internship or industrial attachment to support your general technology, IT, and data work.
+Through my studies and software projects, I have built practical skills in Python, R, Excel, SQL, data analysis, visualization, and basic machine learning, along with experience in web development and technical documentation. I am eager to apply these skills to support your data operations and technology needs while continuing to learn in a practical environment.
+I would like to ask whether you would consider a student intern or industrial attachment placement at this time. If you are not the correct person to speak with regarding this, could you please direct me to the appropriate team member?
+Thank you for your time.
+Kind regards,
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>O041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>C059</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>P060</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Mercy Corps</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Campaign 4 - General Technology Internship</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - technology, IT and data work</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Dear Mercy Corps Team,
+I am a BSc Data Science student at the Open University of Kenya, with an expected graduation year of 2027.
+I am writing to express my interest in an internship or industrial attachment focusing on general technology, IT and data work, aligned with your program monitoring, data collection, research, and digital financial inclusion initiatives such as AgriFin.
+Through my studies and personal projects, I have built skills in Python, R, Excel, SQL, data analysis, visualization, basic machine learning, and software projects. I am looking to apply these foundational technical skills in a practical environment while supporting your team.
+Would you consider an intern or industrial attachment placement for these areas, and could you direct me to the appropriate person if this is handled elsewhere?
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>O042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>C062</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>P061</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Central Bank of Kenya</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Campaign 4 - General Technology Internship</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - data, IT and technology support</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Dear Central Bank of Kenya Team,
+My name is Monica Wughanga Masae, and I am studying for a BSc in Data Science at the Open University of Kenya, with an expected graduation year of 2027.
+I am writing to enquire about internship or industrial attachment opportunities involving technology, IT, and data work, noting your functions in economic research, statistical data collection, financial datasets management, and national payments system oversight.
+Through my studies and personal projects, I have built practical skills in Python, R, SQL, Excel, data analysis, data visualization, basic machine learning, and software development, and I am available to start immediately in Nairobi. I want to contribute to your data and technology tasks while building my practical skills in a professional environment.
+Could you please let me know if you consider interns or industrial attachment students for these areas, and who the appropriate person to contact would be if not you?
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>O043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>C065</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>P063</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>The National Treasury Kenya</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Campaign 2 - Software / Technology Internship</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - software and web development support</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Dear The National Treasury Kenya Team,
+My name is Monica Wughanga Masae, and I am studying for a BSc Data Science at the Open University of Kenya, with an expected graduation year of 2027.
+I am writing to enquire about an internship or industrial attachment placement related to your management of large-scale government financial systems, public investment management platforms, and financial reporting databases.
+Through my studies and personal projects, I have built skills in Python, SQL, web development, and software projects, and I am keen to apply and grow these technical capabilities through application support and software development work.
+I would like to know if you would consider an intern or industrial attachment placement within your technology function, and who I should direct this enquiry to if you do not handle these requests directly.
+Thank you for your time.
+Kind regards,
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>O044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>C069</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>P065</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Kenya Power</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Campaign 2 - Software / Technology Internship</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - software and web development support</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Dear Kenya Power Team,
+I am a BSc Data Science student at the Open University of Kenya, expecting to graduate in 2027.
+I am writing to enquire about internship or industrial attachment opportunities relating to the management of customer self-service portals, digital applications like myPower, and underlying utility data systems.
+Through my coursework and software projects, I have built skills in Python, SQL, web development, and application support. I am looking for a placement where I can apply these technical skills while learning from your team.
+Could you please let me know if you would consider an intern or industrial attachment placement in these areas, and who the appropriate person to speak with would be if this is outside your remit?
+Thank you for your time.
+Kind regards,
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>O045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>C070</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>P066</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Wasoko</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Campaign 2 - Software / Technology Internship</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - software and web development</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Dear Wasoko Team,
+I am a student at the Open University of Kenya studying for a BSc in Data Science, with an expected graduation year of 2027.
+I am writing to enquire about internship or industrial attachment opportunities within your software development, product engineering, and digital retail operations.
+Through my studies and personal projects, I have built skills in Python, R, SQL, web development, and software projects, along with data analysis and basic machine learning. I am looking to contribute to software and web development and application support work while developing my technical skills in a professional setting.
+Could you please let me know if you consider interns or industrial attachment students for these areas, and who I might speak with if there are open positions?
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>O046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>C071</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>P067</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Pezesha</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Campaign 2 - Software / Technology Internship</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - software and web development</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Dear Pezesha Team,
+I am a BSc Data Science student at the Open University of Kenya, expecting to graduate in 2027.
+I am writing to enquire about opportunities for an internship or industrial attachment related to your work in API-driven alternative credit scoring, data point analysis, and digital loan management systems.
+Through my studies and personal projects, I have built skills in Python, R, SQL, software projects, and web development, along with basic machine learning and data analysis. I am looking for a placement where I can contribute to software and web development and application support work while developing my technical skills further.
+Could you let me know if you currently consider interns or industrial attachment students for these areas, and who the appropriate person is to speak with regarding such placements?
+Thank you for your time.
+Kind regards,
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>O047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>C072</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>P069</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>4G Capital</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Campaign 2 - Software / Technology Internship</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - software and web development support</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Dear 4G Capital Team,
+I am a BSc Data Science student at the Open University of Kenya, graduating in 2027.
+I am writing to enquire about opportunities at 4G Capital, which delivers smart business loans, training, and digital financial services using a fintech platform that utilizes AI to right-size loans, alongside mobile money disbursements.
+Through my studies and personal software projects, I have built skills in Python, SQL, web development, and software projects, and I am looking to contribute to software and web development and application support work while developing my technical capabilities further.
+I would like to know if you would consider an intern or industrial attachment placement in these areas, or who I should speak to if these placements are handled elsewhere.
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>O048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>C073</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>P072</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Turaco</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Campaign 4 - General Technology Internship</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Internship enquiry - data, IT, and technology support, BSc Data Science student</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Dear Turaco Team,
+I am a BSc Data Science student at the Open University of Kenya, graduating in 2027, seeking an internship or industrial attachment in Nairobi.
+I am reaching out because Turaco provides microinsurance products through partnerships with top brands and financial institutions, and develops and maintains claims and policy administration technology to support your embedded insurance services.
+Through my studies and software projects, I have built skills in Python, R, SQL, data analysis, data visualization, and basic machine learning, along with technical documentation and reporting. I want to apply these skills to support your technology, IT, and data operations while continuing to learn.
+Could you please let me know if you would consider an intern or industrial attachment placement for these functions, or direct me to the right person to speak with if not?
+Thank you for your time.
+Kind regards,
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>O049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>C076</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>P074</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Campaign 2 - Software / Technology Internship</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - software and web development support</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Dear Glovo Team,
+I am a BSc Data Science student at the Open University of Kenya, graduating in 2027.
+I am writing to enquire about internship or industrial attachment opportunities relating to your digital delivery platform and mobile application.
+Through my studies and personal projects, I have built skills in Python, R, SQL, web development, and software projects, along with data analysis and basic machine learning. I am looking to contribute to your software and web development or application support work while developing my technical skills further in a professional environment.
+Could you please let me know if you consider students for internship or industrial attachment placements, or point me to the right person to contact regarding this?
+Thank you for your time.
+Kind regards,
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>O050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>C077</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>P075</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bolt</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Campaign 2 - Software / Technology Internship</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - software and web development support</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Dear Bolt Team,
+I am a student at the Open University of Kenya studying for a BSc in Data Science, with an expected graduation in 2027.
+I am reaching out regarding potential internship or industrial attachment opportunities because your technology function involves software development, data operations, and AI-powered urban mobility features.
+Through my studies and software projects, I have built skills in Python, R, SQL, and web development, alongside data analysis and reporting. I am looking to apply these technical skills and learn practical software and web development processes in a professional environment.
+Could you please let me know if you consider students for internships or industrial attachments, or direct me to the correct person to speak with regarding these roles?
+Thank you for your time.
+Kind regards,
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T1"/>
+  <autoFilter ref="A1:T51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10213,7 +13345,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1"/>
+  <autoFilter ref="A1:B15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId2"/>

--- a/data/internship_outreach.xlsx
+++ b/data/internship_outreach.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Settings" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$AA$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Contacts'!$A$1:$L$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$AA$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Contacts'!$A$1:$L$90</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Outreach'!$A$1:$T$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Settings'!$A$1:$B$15</definedName>
   </definedNames>
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA78"/>
+  <dimension ref="A1:AA88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5019,9 +5019,65 @@
           <t>AI Logistics Software</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://leta.ai/careers</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Data Science Intern; Data Analyst; Software/Web Development Intern</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>10</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>10</v>
+      </c>
+      <c r="V45" t="n">
+        <v>37</v>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>The evidence retrieved from the website and careers page only contains a verification message ('Please wait while your request is being verified...'), making it impossible to evaluate the organisation's actual operations, technology function, or internship opportunities.</t>
+        </is>
+      </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NEEDS_REVIEW</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
@@ -5066,9 +5122,65 @@
           <t>AgriTech</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>BETA Agriculture Technologies provides digital solutions powered by AI, IoT, satellite monitoring, and precision farming technologies for farmers, agribusinesses, and financial institutions in East Africa.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Deployment of AI-powered agronomy, satellite monitoring, IoT smart sensors, and data analytics for agriculture.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Data Analyst Intern; Data Science Intern; Data/Research Assistant; AI/ML Intern</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>10</v>
+      </c>
+      <c r="R46" t="n">
+        <v>17</v>
+      </c>
+      <c r="S46" t="n">
+        <v>7</v>
+      </c>
+      <c r="T46" t="n">
+        <v>7</v>
+      </c>
+      <c r="U46" t="n">
+        <v>10</v>
+      </c>
+      <c r="V46" t="n">
+        <v>73</v>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>BETA Agriculture Technologies is based in Nairobi and focuses on digital solutions powered by AI, IoT, satellite monitoring, and precision farming technologies. The student's skills in Python, data analysis, machine learning, and data visualization align well with the company's data-driven agricultural intelligence platforms, though no explicit internship programme was found.</t>
+        </is>
+      </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>QUALIFY</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
@@ -5113,9 +5225,65 @@
           <t>Digital Solutions / AgriTech</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://agrikenya.co.ke/careers</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>5</v>
+      </c>
+      <c r="R47" t="n">
+        <v>10</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>5</v>
+      </c>
+      <c r="V47" t="n">
+        <v>37</v>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>The evidence retrieval for both the main website and careers page only returned verification messages and did not load any content about the organisation's operations, technology functions, or contact channels. As a result, there is insufficient evidence to confirm whether a professional technology or data internship can be supported.</t>
+        </is>
+      </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NEEDS_REVIEW</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
@@ -5160,9 +5328,65 @@
           <t>Fintech / InsurTech</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Insurtech Forum Nairobi operates as a platform and forum connecting insurance professionals, tech innovators, startups, and investors to explore AI, ML, and insurtech solutions.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Hosting events, workshops, and discussions focused on AI, machine learning, and data analytics within the insurance sector.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data/Research Assistant; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>5</v>
+      </c>
+      <c r="R48" t="n">
+        <v>10</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="n">
+        <v>5</v>
+      </c>
+      <c r="U48" t="n">
+        <v>10</v>
+      </c>
+      <c r="V48" t="n">
+        <v>50</v>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>The evidence shows that Insurtech Forum Nairobi is an annual forum and platform focusing on insurance innovation, AI, ML, and data analytics, but it lacks any evidence of an internal technical team, ongoing operations outside of event hosting, or student internship programmes.</t>
+        </is>
+      </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NEEDS_REVIEW</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -5207,9 +5431,65 @@
           <t>InsurTech</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Bolttech operates an international insurtech business offering a B2B2C protection and insurance platform.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Development of B2B2C insurance platforms, embedded insurance APIs, data insights, and digital distribution engines.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>The careers section invites candidates to join their team, though specific student internship programmes are not detailed in the text.</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://bolttech.io/careers/</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Business Intelligence Analyst; Software/Web Development Intern; Data Operations Assistant</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>10</v>
+      </c>
+      <c r="R49" t="n">
+        <v>18</v>
+      </c>
+      <c r="S49" t="n">
+        <v>9</v>
+      </c>
+      <c r="T49" t="n">
+        <v>8</v>
+      </c>
+      <c r="U49" t="n">
+        <v>8</v>
+      </c>
+      <c r="V49" t="n">
+        <v>78</v>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Bolttech is an international insurtech business providing a B2B2C protection and insurance platform featuring APIs, data insights, and embedded insurance solutions, offering strong technical relevance for a data science student. While the evidence mentions a 'Careers' link pointing to a team of pioneers, it lacks specific student internship programme details, resulting in a moderate internship likelihood score.</t>
+        </is>
+      </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>QUALIFY</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
@@ -5254,9 +5534,65 @@
           <t>UN agency / Humanitarian data</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>The World Food Programme delivers food assistance in emergencies and supports sustainable and resilient livelihoods to achieve global food security.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>The organisation utilizes digital transformation, data analysis, resources and data publications, and food security analysis.</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>The careers section invites candidates to view job opportunities, though specific student internship postings are not explicitly detailed in the sampled text.</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://www.wfp.org/careers</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Data/Research Assistant; Business Intelligence; Data Operations</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>15</v>
+      </c>
+      <c r="R50" t="n">
+        <v>18</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="n">
+        <v>8</v>
+      </c>
+      <c r="U50" t="n">
+        <v>10</v>
+      </c>
+      <c r="V50" t="n">
+        <v>79</v>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>The World Food Programme is a large international organisation that engages in global humanitarian work, data analysis, and digital transformation initiatives such as innovation and digital technology. The retrieved text links to a careers section with job opportunities and mentions areas like resources, data, and food security analysis which align well with the student's data science background. Contactability is supported via their main website and careers portal.</t>
+        </is>
+      </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>QUALIFY</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
@@ -5301,9 +5637,65 @@
           <t>UN agency / Health data</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>The World Health Organization directs and coordinates international health within the United Nations system.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Global health data collection, dashboards, data hubs, statistical estimation, and public health surveillance.</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>The careers page explicitly mentions early-career and professional opportunities, including pathways for health research assistants and data managers.</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>https://www.who.int/careers</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Data/Research Assistant; Business Intelligence; Data Operations</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>18</v>
+      </c>
+      <c r="R51" t="n">
+        <v>18</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="n">
+        <v>9</v>
+      </c>
+      <c r="U51" t="n">
+        <v>8</v>
+      </c>
+      <c r="V51" t="n">
+        <v>83</v>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>The World Health Organization runs data hubs, global health estimates, dashboards, and surveillance operations that directly match data science and analytics skills. The evidence includes a dedicated careers portal and references to data managers and research assistants, supporting a strong technical and data-focused internship environment.</t>
+        </is>
+      </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>QUALIFY</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
@@ -5348,9 +5740,65 @@
           <t>International finance / Development data</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>An international financial institution that provides loans, advice, and research to developing countries to reduce poverty and promote development.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Research, data analysis, development data platforms, and economic modeling.</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://www.worldbank.org/ext/en/jobs</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Data/Research Assistant; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>15</v>
+      </c>
+      <c r="R52" t="n">
+        <v>18</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="n">
+        <v>8</v>
+      </c>
+      <c r="U52" t="n">
+        <v>10</v>
+      </c>
+      <c r="V52" t="n">
+        <v>79</v>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>The World Bank is a major global institution with extensive data and research initiatives, as evidenced by its focus on data for development and publications like the World Development Report on AI. The student's background in Data Science aligns well with the organization's heavy reliance on data analysis, research, and economic reporting.</t>
+        </is>
+      </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>QUALIFY</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
@@ -5395,9 +5843,65 @@
           <t>Humanitarian / Emergency data systems</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>The Kenya Red Cross Society is a humanitarian relief organization that works to alleviate human suffering, manage disasters, and provide health and community services.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>The careers page lists Training Opportunities and Volunteer Opportunities.</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>https://redcross.or.ke/careers/</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data/Research Assistant; Business Intelligence; Data Operations; Reporting</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>15</v>
+      </c>
+      <c r="R53" t="n">
+        <v>14</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="n">
+        <v>10</v>
+      </c>
+      <c r="U53" t="n">
+        <v>10</v>
+      </c>
+      <c r="V53" t="n">
+        <v>69</v>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>The Kenya Red Cross Society is a large established humanitarian organization based in Nairobi with a dedicated careers page and training/volunteer opportunities, providing a plausible institutional setting for data analysis or reporting tasks, although specific technology or data teams are not detailed in the web text.</t>
+        </is>
+      </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>QUALIFY</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
@@ -5442,9 +5946,65 @@
           <t>Health NGO / Health informatics</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Amref Health Africa works with communities and governments to strengthen health systems and advance African-led health solutions.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Monitoring and evaluation, research, and data operations supporting health programmes.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>The careers section lists categories for volunteers and future jobs.</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>https://amref.org/careers/</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data/Research Assistant; Business Intelligence; Data Operations</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>18</v>
+      </c>
+      <c r="R54" t="n">
+        <v>16</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="n">
+        <v>9</v>
+      </c>
+      <c r="U54" t="n">
+        <v>10</v>
+      </c>
+      <c r="V54" t="n">
+        <v>81</v>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Amref Health Africa is a major multinational health organization based in Nairobi with a careers section and mentions of volunteers and future jobs, providing potential opportunities for data and research assistant roles.</t>
+        </is>
+      </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>QUALIFY</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
@@ -5489,9 +6049,65 @@
           <t>Global health NGO / Health data</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>PATH transforms innovative ideas into global health breakthroughs, operating in over 70 countries including Kenya.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>AI, data, and digital health systems strengthening</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Searching worldwide for passionate emerging professionals in disciplines from science and engineering to information technology</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>https://www.path.org/who-we-are/careers/</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Data/Research Assistant; Business Intelligence; Data Operations</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>18</v>
+      </c>
+      <c r="R55" t="n">
+        <v>18</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="n">
+        <v>9</v>
+      </c>
+      <c r="U55" t="n">
+        <v>10</v>
+      </c>
+      <c r="V55" t="n">
+        <v>85</v>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>PATH operates in Kenya and features an AI, data, and digital health systems strengthening function along with a dedicated careers page that mentions searching for emerging professionals in disciplines including information technology.</t>
+        </is>
+      </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>QUALIFY</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
@@ -5536,9 +6152,65 @@
           <t>Global health NGO / M&amp;E</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Population Services International is a global network of locally-led organizations focused on transforming health by tackling root causes and delivering healthcare products and services.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Digital health initiatives, health systems data management, and global network systems.</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>The careers page provides access to active global job postings and recruitment processes, though specific student internship programs are not explicitly detailed on the main page.</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>https://www.psi.org/careers/</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Data/Research Assistant; Business Intelligence; Data Operations</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>15</v>
+      </c>
+      <c r="R56" t="n">
+        <v>16</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="n">
+        <v>9</v>
+      </c>
+      <c r="U56" t="n">
+        <v>8</v>
+      </c>
+      <c r="V56" t="n">
+        <v>76</v>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Population Services International is an international non-governmental organization working in health systems strengthening and digital health with a presence across multiple countries including Kenya, offering strong alignment for data science and tech roles via its digital health capabilities and careers portal.</t>
+        </is>
+      </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>QUALIFY</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
@@ -5583,9 +6255,65 @@
           <t>Humanitarian NGO / M&amp;E</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>CARE International is an international humanitarian aid and development organization dedicated to ending poverty and providing emergency support.</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>The evidence does not detail specific internal software engineering or data teams, but large international NGOs typically maintain data and research operations.</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>The careers page explicitly features a 'Search for Internships' link.</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>https://www.care.org/careers/</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data/Research Assistant; Data Science Intern; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>18</v>
+      </c>
+      <c r="R57" t="n">
+        <v>15</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="n">
+        <v>8</v>
+      </c>
+      <c r="U57" t="n">
+        <v>8</v>
+      </c>
+      <c r="V57" t="n">
+        <v>71</v>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>CARE International is a large global humanitarian and development organization that provides careers and internship search pages, making it a plausible host for data and research roles, though its primary focus is humanitarian aid rather than software engineering.</t>
+        </is>
+      </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>QUALIFY</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
@@ -5630,9 +6358,65 @@
           <t>Humanitarian NGO / Research</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Oxfam is a global organization working to challenge inequality, fight poverty, and respond to humanitarian crises.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>https://www.oxfam.org/en/take-action/jobs</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data/Research Assistant; Business Intelligence; Reporting</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>15</v>
+      </c>
+      <c r="R58" t="n">
+        <v>12</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="n">
+        <v>8</v>
+      </c>
+      <c r="U58" t="n">
+        <v>8</v>
+      </c>
+      <c r="V58" t="n">
+        <v>63</v>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Oxfam is a large international confederation with operations in Kenya and a dedicated careers portal, offering potential paths for data or research roles aligned with a BSc in Data Science. However, the evidence does not specifically detail a standalone technology or software development team at the local country office, making it a general organizational placement rather than a core tech firm.</t>
+        </is>
+      </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>QUALIFY</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
@@ -5677,9 +6461,65 @@
           <t>Development NGO / M&amp;E</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>ActionAid is a global federation working for a world free from poverty and injustice.</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>https://actionaid.org/jobs</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data/Research Assistant; Business Intelligence; IT Support</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>5</v>
+      </c>
+      <c r="R59" t="n">
+        <v>10</v>
+      </c>
+      <c r="S59" t="n">
+        <v>8</v>
+      </c>
+      <c r="T59" t="n">
+        <v>5</v>
+      </c>
+      <c r="U59" t="n">
+        <v>8</v>
+      </c>
+      <c r="V59" t="n">
+        <v>46</v>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>ActionAid is a global federation focused on social justice, women's rights, and poverty alleviation, with a jobs page that currently lists no vacancies. While large international NGOs often maintain IT, data, or research functions, the provided evidence does not detail an internal technology or data department.</t>
+        </is>
+      </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NEEDS_REVIEW</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
@@ -5724,9 +6564,65 @@
           <t>Humanitarian NGO / Data and evidence</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>An international humanitarian organisation working alongside communities to meet urgent needs and create conditions for lasting progress.</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Research, data management, and program monitoring and evaluation supporting global humanitarian initiatives.</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>The careers page lists country-specific job boards, a talent database, and consultancy opportunities.</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>https://www.prosperglobal.org/careers</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data/Research Assistant; Data Operations; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>18</v>
+      </c>
+      <c r="R60" t="n">
+        <v>16</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="n">
+        <v>9</v>
+      </c>
+      <c r="U60" t="n">
+        <v>8</v>
+      </c>
+      <c r="V60" t="n">
+        <v>76</v>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Prosper Global (formerly Mercy Corps) is a large international humanitarian organization that runs country-specific job boards and maintains local operations in Nairobi, Kenya. The evidence demonstrates established organisational maturity, a structured careers section, and potential data-related or research roles via country-specific opportunities.</t>
+        </is>
+      </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>QUALIFY</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
@@ -5771,9 +6667,65 @@
           <t>Government / National ICT</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Data Science Intern; Data Analyst; IT Support; Technology Intern</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>5</v>
+      </c>
+      <c r="R61" t="n">
+        <v>10</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>10</v>
+      </c>
+      <c r="V61" t="n">
+        <v>45</v>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>The evidence retrieval failed due to an SSL certificate error on the website, so the organisation's current operations and internship programs could not be checked. However, the name ICT Authority Kenya suggests a government technology agency based in Nairobi, which aligns with the student's geographic preference and target technology roles, but requires manual verification.</t>
+        </is>
+      </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NEEDS_REVIEW</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
@@ -5818,9 +6770,65 @@
           <t>Government / Official statistics</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data/Research Assistant; Data Science Intern</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>10</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>10</v>
+      </c>
+      <c r="V62" t="n">
+        <v>40</v>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>The evidence retrieval failed due to an SSL certificate error on the organisation's website, meaning no website evidence could be checked. However, based on the organisation's name as a national statistical agency, it likely handles data and research, but review is needed due to the lack of accessible evidence.</t>
+        </is>
+      </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NEEDS_REVIEW</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
@@ -5865,9 +6873,65 @@
           <t>Government / Financial data</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>The Central Bank of Kenya is responsible for formulating monetary policy, promoting financial stability, issuing currency, and acting as the fiscal agent of the Government.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Research, macroeconomic statistics, financial data reporting, and national payments system oversight.</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>The Central Bank of Kenya has been running an Internship Program that takes six (6) months, requiring a first degree in disciplines including Statistics.</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>https://www.centralbank.go.ke/cbkcareers/</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Data/Research Assistant; Business Intelligence; Data Operations</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>25</v>
+      </c>
+      <c r="R63" t="n">
+        <v>18</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="n">
+        <v>10</v>
+      </c>
+      <c r="U63" t="n">
+        <v>10</v>
+      </c>
+      <c r="V63" t="n">
+        <v>91</v>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>The Central Bank of Kenya explicitly runs an established Internship Program and lists relevant disciplines including Statistics and Finance. The organization manages significant financial statistics, data reporting, and national payments systems in Nairobi, perfectly aligning with the student's BSc Data Science background.</t>
+        </is>
+      </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>QUALIFY</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
@@ -5912,9 +6976,65 @@
           <t>Government regulator / Telecom data</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>The organisation handles competition law, policy, and consumer protection in Kenya.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>The careers page references a vacancy table and online job applications, but lists no specific active internship programmes in the text.</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>https://cak.go.ke/careers</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data/Research Assistant; IT Support</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>10</v>
+      </c>
+      <c r="R64" t="n">
+        <v>10</v>
+      </c>
+      <c r="S64" t="n">
+        <v>8</v>
+      </c>
+      <c r="T64" t="n">
+        <v>8</v>
+      </c>
+      <c r="U64" t="n">
+        <v>10</v>
+      </c>
+      <c r="V64" t="n">
+        <v>56</v>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>The evidence shows the organisation has a careers page with a vacancy listings section, but the main text and metadata indicate it is the Competition Authority of Kenya focusing on competition law, consumer protection, and market regulation, while the scraped website text has been heavily compromised by spam/gambling injections. Because the actual technical functions and current internship opportunities cannot be reliably verified due to compromised site content, the application requires manual review.</t>
+        </is>
+      </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NEEDS_REVIEW</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
@@ -5959,9 +7079,65 @@
           <t>Government / Health insurance systems</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>https://nhif.or.ke/careers</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; IT Support; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>5</v>
+      </c>
+      <c r="R65" t="n">
+        <v>10</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="n">
+        <v>5</v>
+      </c>
+      <c r="U65" t="n">
+        <v>10</v>
+      </c>
+      <c r="V65" t="n">
+        <v>50</v>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>The evidence retrieval for the website and careers page was blocked by a verification screen, leaving the specific technology functions and internship programmes unverified. However, as a national fund, it is likely to maintain IT and data operations that could potentially match the student's background.</t>
+        </is>
+      </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NEEDS_REVIEW</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
@@ -6006,9 +7182,65 @@
           <t>Government / Public finance data</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>The National Treasury formulates, implements, and monitors macroeconomic policies and manages public finances in Kenya.</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Manages national financial systems including the Integrated Financial Management System (IFMS) and economic data reporting.</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Young Professional Officer Recruitment listed on the vacancies portal.</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>https://treasury.go.ke/vacancy</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data/Research Assistant; Business Intelligence; Data Operations; IT Support</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>18</v>
+      </c>
+      <c r="R66" t="n">
+        <v>16</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="n">
+        <v>9</v>
+      </c>
+      <c r="U66" t="n">
+        <v>10</v>
+      </c>
+      <c r="V66" t="n">
+        <v>78</v>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>The National Treasury Kenya is an established public sector institution based in Nairobi that manages national economic and financial matters, including systems like the Integrated Financial Management System. The website lists opportunities such as Young Professional Officer roles and vacancies, offering a suitable environment for data and technology attachments in alignment with the student's background.</t>
+        </is>
+      </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>QUALIFY</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
@@ -6053,9 +7285,65 @@
           <t>County government / Public services data</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; IT Support; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>5</v>
+      </c>
+      <c r="R67" t="n">
+        <v>10</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>10</v>
+      </c>
+      <c r="V67" t="n">
+        <v>40</v>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>The evidence retrieval failed due to an SSL certificate error on the website, leaving no verifiable text about the organization's current technical functions or internship opportunities. While government entities like Nairobi City County typically maintain IT or data operations, the lack of evidence prevents a confident assessment.</t>
+        </is>
+      </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NEEDS_REVIEW</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
@@ -6100,9 +7388,65 @@
           <t>Government agency / Infrastructure data</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>https://kenha.co.ke/careers</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Data Analyst; IT Support; Data Science Intern</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>5</v>
+      </c>
+      <c r="R68" t="n">
+        <v>10</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="n">
+        <v>5</v>
+      </c>
+      <c r="U68" t="n">
+        <v>10</v>
+      </c>
+      <c r="V68" t="n">
+        <v>50</v>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>The evidence block only shows verification challenges ('Please wait while your request is being verified...') for both the main website and careers page. Consequently, specific technology functions and internship opportunities could not be verified from the provided evidence.</t>
+        </is>
+      </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NEEDS_REVIEW</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
@@ -6147,9 +7491,65 @@
           <t>Government / Training and skills data</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>https://nita.go.ke/careers</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; IT Support</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>5</v>
+      </c>
+      <c r="R69" t="n">
+        <v>10</v>
+      </c>
+      <c r="S69" t="n">
+        <v>8</v>
+      </c>
+      <c r="T69" t="n">
+        <v>5</v>
+      </c>
+      <c r="U69" t="n">
+        <v>10</v>
+      </c>
+      <c r="V69" t="n">
+        <v>48</v>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>The evidence retrieved from the website and careers page was blocked with a verification message, preventing any check of current technology functions, internship programmes, or contact methods. The organisation is known from its name to be a national training authority in Kenya, but lack of accessible web evidence requires a review.</t>
+        </is>
+      </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NEEDS_REVIEW</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
@@ -6194,9 +7594,65 @@
           <t>Utility / Energy data systems</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Kenya Power is a national utility operating most of Kenya's electricity transmission and distribution.</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Manages digital services, self-service portals, and the myPower app for electricity consumers.</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Careers link found on the website, though no explicit internship program details were provided in the text.</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>https://kplc.co.ke</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Business Intelligence; Data Operations; IT Support; Software/Web Development</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>10</v>
+      </c>
+      <c r="R70" t="n">
+        <v>16</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="n">
+        <v>8</v>
+      </c>
+      <c r="U70" t="n">
+        <v>10</v>
+      </c>
+      <c r="V70" t="n">
+        <v>72</v>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Kenya Power operates national electricity transmission and distribution networks, utilizing self-service portals and apps such as myPower, offering relevant data and IT roles. Evidence includes a website with navigation options including Careers, though specific intern openings are not detailed in the text. The organization is based in Nairobi, matching the student's preferred location.</t>
+        </is>
+      </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>QUALIFY</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
@@ -6241,9 +7697,65 @@
           <t>B2B e-commerce startup / Logistics tech</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Wasoko operates a B2B e-commerce platform transforming access to essential goods and services across Africa.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Software development and technology solutions built by product and engineering teams to support informal retail supply chains.</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>The careers page actively recruits new employees and features testimonials from engineering staff regarding career growth and learning opportunities.</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>https://wasoko.com/careers/</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Software/Web Development Intern; Business Intelligence Intern; Data Operations Assistant</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>18</v>
+      </c>
+      <c r="R71" t="n">
+        <v>16</v>
+      </c>
+      <c r="S71" t="n">
+        <v>9</v>
+      </c>
+      <c r="T71" t="n">
+        <v>8</v>
+      </c>
+      <c r="U71" t="n">
+        <v>10</v>
+      </c>
+      <c r="V71" t="n">
+        <v>81</v>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Wasoko is a major B2B e-commerce and technology company with an active engineering department in Nairobi, featuring staff such as a Front End Engineer and Head of Engineering who work on software solutions for informal retail. The careers pages show explicit hiring intent and remote/hybrid work options, aligning well with the student's background in data science, software, and web development.</t>
+        </is>
+      </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>QUALIFY</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
@@ -6288,9 +7800,65 @@
           <t>Fintech startup / Embedded lending</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Pezesha operates an AI-powered SME lending platform and digital credit infrastructure connecting MSMEs to working capital.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>API-driven alternative credit scoring, AI-powered financial literacy tools, and loan management software development.</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>The careers page lists 'Internship Program', 'Software Engineer Intern', 'QA Engineer Intern', and 'Junior Data Scientist'.</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>https://pezesha.com/careers/</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Data Science Intern; Junior Data Scientist; Software Engineer Intern; Data Analyst</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>25</v>
+      </c>
+      <c r="R72" t="n">
+        <v>20</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="n">
+        <v>10</v>
+      </c>
+      <c r="U72" t="n">
+        <v>10</v>
+      </c>
+      <c r="V72" t="n">
+        <v>100</v>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>The evidence explicitly lists an 'Internship Program', 'Junior Data Scientist', 'Software Engineer Intern', and 'QA Engineer Intern' on their careers page. Their platform relies on AI-powered credit scoring, APIs, and alternative data, making it an exceptional match for a BSc Data Science student's skills in Python, SQL, and data analysis.</t>
+        </is>
+      </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>QUALIFY</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
@@ -6335,9 +7903,65 @@
           <t>Fintech / Micro-lending data</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>4G Capital delivers smart business loans, training, and digital financial services to empower small businesses across Africa.</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>The organization uses AI and digital financial platforms to right-size loans and manage mobile money disbursements.</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>The careers page mentions 'View Open Roles' and a testimonial explicitly notes an employee's journey 'From intern to Customer Care Manager'.</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>https://www.4g-capital.com/workwithus</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Data/Research Assistant; Business Intelligence; Application Support</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>18</v>
+      </c>
+      <c r="R73" t="n">
+        <v>18</v>
+      </c>
+      <c r="S73" t="n">
+        <v>9</v>
+      </c>
+      <c r="T73" t="n">
+        <v>9</v>
+      </c>
+      <c r="U73" t="n">
+        <v>10</v>
+      </c>
+      <c r="V73" t="n">
+        <v>84</v>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>4G Capital is a fintech organization operating in Kenya with a dedicated careers page and explicit mentions of utilizing AI and digital financial services. The evidence specifically references a career progression story from intern to manager, supporting the likelihood of hosting interns in data, technology, or analytics roles.</t>
+        </is>
+      </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>QUALIFY</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
@@ -6382,9 +8006,65 @@
           <t>Insurtech startup</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Turaco provides simple, affordable and technology-enabled microinsurance products through partnerships with top brands.</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Trusted claims and policy administration technology.</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>The careers page states they are 'always seeking great people to help Turaco grow as we scale' and offers work opportunities across several disciplines including engineering.</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>https://turaco.breezy.hr/</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Data/Research Assistant; Business Intelligence; Data Operations; Software/Web Development</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>15</v>
+      </c>
+      <c r="R74" t="n">
+        <v>15</v>
+      </c>
+      <c r="S74" t="n">
+        <v>9</v>
+      </c>
+      <c r="T74" t="n">
+        <v>9</v>
+      </c>
+      <c r="U74" t="n">
+        <v>10</v>
+      </c>
+      <c r="V74" t="n">
+        <v>76</v>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Turaco operates as a technology-enabled microinsurance company with a dedicated engineering discipline mentioned in their careers and culture description, and they maintain a careers portal hosted on Breezy HR with a physical office presence in Nairobi. While current listed openings focus on operations, partnerships, and business development rather than direct software roles, the company's tech-focused nature and Nairobi location offer a solid potential fit for data and technology attachments.</t>
+        </is>
+      </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>QUALIFY</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
@@ -6429,9 +8109,65 @@
           <t>E-commerce / Marketplace data</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Operates an online e-commerce marketplace and retail platform in Kenya.</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>E-commerce platform development, database management, digital payment processing, and web/application operations.</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>https://www.jumia.co.ke/mizani-25-miracle-nourishing-hair-oil-125ml-provides-lightweight-hydration-shine-frizz-control-infused-with-coconut-and-jojoba-oil-to-enhance-softness-and-manageability-for-all-hair-types-33638355.html</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Data Analyst Intern; Data Science Intern; Software/Web Development Intern; Business Intelligence Intern; Data Operations Intern</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>15</v>
+      </c>
+      <c r="R75" t="n">
+        <v>16</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="n">
+        <v>7</v>
+      </c>
+      <c r="U75" t="n">
+        <v>10</v>
+      </c>
+      <c r="V75" t="n">
+        <v>78</v>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Jumia Kenya operates as a major e-commerce platform in Nairobi with extensive digital infrastructure, data operations, and web development functions that align well with data science and software roles. While specific internship programmes are not detailed in the scraped catalog pages, large e-commerce companies frequently support technical attachments and data analytics roles.</t>
+        </is>
+      </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>QUALIFY</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
@@ -6476,9 +8212,65 @@
           <t>Ride-hailing / Mobility tech</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>5</v>
+      </c>
+      <c r="V76" t="n">
+        <v>5</v>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>No evidence was retrieved because the domain did not resolve. Therefore, the organisation could not be checked.</t>
+        </is>
+      </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NEEDS_REVIEW</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
@@ -6523,9 +8315,65 @@
           <t>Delivery platform / Logistics data</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Operates an on-demand delivery platform connecting users with local restaurants, grocery stores, supermarkets, and pharmacies.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Maintains a mobile and web application platform supporting order placement, real-time tracking, and multi-category logistics technology.</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>The website provides a dedicated 'Careers' link with the prompt 'Ready for an exciting new challenge? If you’re ambitious, humble, and love working with others, then we want to hear from you!'</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>https://careers.glovoapp.com/</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Software/Web Development; Business Intelligence; Data Operations</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>15</v>
+      </c>
+      <c r="R77" t="n">
+        <v>16</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="n">
+        <v>9</v>
+      </c>
+      <c r="U77" t="n">
+        <v>10</v>
+      </c>
+      <c r="V77" t="n">
+        <v>80</v>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Glovo operates a technology platform for multi-category delivery services with operations in Kenya and explicitly lists a careers section on their website, providing a suitable environment for technology and data roles.</t>
+        </is>
+      </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>QUALIFY</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
@@ -6570,9 +8418,65 @@
           <t>Ride-hailing / Mobility data</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Bolt provides a transport and delivery platform offering ride-hailing, shared scooters, e-bikes, and food/grocery delivery.</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Software engineering, product development, data analytics, and artificial intelligence systems for transport and logistics.</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>The careers page offers a structured application process ('Step 1. Application ... Find a role that interests you and submit your application') across major tech hubs and operational regions.</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>https://bolt.eu/en/careers/</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Data Science Intern; Data Analyst; Software/Web Development Intern; Business Intelligence Intern; AI/ML Intern</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>18</v>
+      </c>
+      <c r="R78" t="n">
+        <v>18</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="n">
+        <v>10</v>
+      </c>
+      <c r="U78" t="n">
+        <v>8</v>
+      </c>
+      <c r="V78" t="n">
+        <v>89</v>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Bolt is a major technology company operating platforms for ride-hailing, scooters, and food delivery with significant engineering, product, and AI initiatives. The evidence shows a dedicated careers portal and a global technology team, aligning well with the student's background in data science, software development, and AI applications.</t>
+        </is>
+      </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>QUALIFY</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
@@ -6586,8 +8490,1038 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>C078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Ackyshine Monitoring and Evaluation Consultancy</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://ackyshine.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Ackyshine operates an AI-integrated digital platform providing personal productivity, learning, analytics, and AI-powered assistance tools.</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Development and maintenance of an AI-integrated digital platform involving data dashboards, modules, and AI support.</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>https://mobile.ackyshine.com/careers</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Data Science Intern; Data Analyst; AI/ML Intern; Software/Web Development Intern; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>10</v>
+      </c>
+      <c r="R79" t="n">
+        <v>18</v>
+      </c>
+      <c r="S79" t="n">
+        <v>7</v>
+      </c>
+      <c r="T79" t="n">
+        <v>6</v>
+      </c>
+      <c r="U79" t="n">
+        <v>10</v>
+      </c>
+      <c r="V79" t="n">
+        <v>74</v>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Ackyshine develops an AI-integrated digital platform featuring personal productivity, analytics, and AI-powered assistance, offering a strong technical environment matching the student's data science skills. However, the retrieved pages do not contain specific internship listings or formal student programmes, yielding a moderate score.</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>Search: monitoring and evaluation consultancy</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>C079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Lambda Partners</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://lambdapartners.org</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="n">
+        <v>5</v>
+      </c>
+      <c r="V80" t="n">
+        <v>5</v>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>The website access was blocked with an HTTP 403 error, resulting in no retrieved evidence about the organisation's operations, technology function, or internship opportunities.</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>Search: monitoring and evaluation consultancy</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>C080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Xyvra Consultancy Group</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://xyvraconsultancy.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="n">
+        <v>5</v>
+      </c>
+      <c r="V81" t="n">
+        <v>5</v>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>NO EVIDENCE RETRIEVED. The website access was blocked by the website with an HTTP 403 error, leaving no evidence to assess technology relevance, internship likelihood, or other criteria.</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>Search: monitoring and evaluation consultancy</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>C081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>RVS Kenya</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://www.rvskenya.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>https://www.rvskenya.com/careers</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="n">
+        <v>5</v>
+      </c>
+      <c r="V82" t="n">
+        <v>5</v>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>The evidence retrieved from the website and careers page only returned verification challenge messages, leaving the organisation's operations and technology functions unknown.</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>Search: monitoring and evaluation consultancy</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>C082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Hoffman Solutions</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://hoffmansolutions.co.ke</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>https://hoffmansolutions.co.ke/careers</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="n">
+        <v>10</v>
+      </c>
+      <c r="V83" t="n">
+        <v>10</v>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>The evidence block only shows verification screens stating 'Please wait while your request is being verified...' for both the main website and careers page. Because the content could not be accessed, there is insufficient evidence to determine the technology function or internship opportunities.</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>Search: monitoring and evaluation consultancy</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>C083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Third Party Monitoring and Evaluation Limited</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://thirdpartymonitoring.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>The organisation provides project monitoring, evaluation, learning, research, and data analytics services.</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Data analytics, data visualizations, M&amp;E systems, automated research tools coding, and cloud data hosting.</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>The website includes dedicated navigation links for 'Careers' and 'Job Opportunities'.</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>https://thirdpartymonitoring.com/careers/</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Data/Research Assistant; Business Intelligence Intern; Data Operations Intern</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>12</v>
+      </c>
+      <c r="R84" t="n">
+        <v>18</v>
+      </c>
+      <c r="S84" t="n">
+        <v>8</v>
+      </c>
+      <c r="T84" t="n">
+        <v>8</v>
+      </c>
+      <c r="U84" t="n">
+        <v>10</v>
+      </c>
+      <c r="V84" t="n">
+        <v>76</v>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Third Party Monitoring and Evaluation Limited (also appearing as Firstdata) offers data analytics, M&amp;E systems, and ICT support with Python, SQL, and PowerBI capabilities, aligning well with a data science student's skills. The website features dedicated Careers and Job Opportunities links, providing a reachable contact route in Nairobi.</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>Search: monitoring and evaluation consultancy</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>C084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Advantech Consulting</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://advantech.co.ke</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>https://advantech.co.ke/careers</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data Science Intern; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>10</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" t="n">
+        <v>5</v>
+      </c>
+      <c r="V85" t="n">
+        <v>30</v>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>The website evidence for Advantech Consulting returned verification blocks stating 'Please wait while your request is being verified...', preventing any assessment of their actual technology operations or contact details.</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>Search: monitoring and evaluation consultancy</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>C085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>MNC Consulting</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://mncconsulting.co.ke</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>MNC Consulting is a professional consultancy firm offering audit, tax, human resource management, business advisory, and communication services such as USSD and Bulk SMS.</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Communication services (USSD, Bulk SMS, Short Codes) and digital HR modules including HR Analytics.</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>The careers page at hr.mncconsulting.co.ke/careers/ features recruitment statements inviting talent to explore opportunities and submit applications.</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>https://hr.mncconsulting.co.ke/careers/</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Data Analyst; Data/Research Assistant; Business Intelligence; Software/Web Development</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>15</v>
+      </c>
+      <c r="R86" t="n">
+        <v>14</v>
+      </c>
+      <c r="S86" t="n">
+        <v>8</v>
+      </c>
+      <c r="T86" t="n">
+        <v>9</v>
+      </c>
+      <c r="U86" t="n">
+        <v>10</v>
+      </c>
+      <c r="V86" t="n">
+        <v>71</v>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>MNC Consulting provides business and communication services including USSD, Bulk SMS, and short codes, and operates an HR module featuring HR Analytics, offering viable technology and data roles in Nairobi with accessible contact routes.</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>QUALIFY</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>Search: monitoring and evaluation consultancy</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>C086</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Edgeways Consultancy</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://edgewaysconsultants.co.ke</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Edgeways Consultancy is a consulting firm focused on growing organizations through leadership training, executive coaching, and various sector consultancies.</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>https://edgewaysconsultants.co.ke/careers/</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>5</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="n">
+        <v>5</v>
+      </c>
+      <c r="U87" t="n">
+        <v>5</v>
+      </c>
+      <c r="V87" t="n">
+        <v>20</v>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Edgeways Consultancy is a leadership and management consulting firm offering training, executive coaching, and consultancy services in areas such as security, health, and climate change. The evidence does not show any core technology, software development, or data science functions, and the listed career opportunities are in fields like marketing, finance, and customer care located internationally.</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>Search: monitoring and evaluation consultancy</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>C087</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ICPRS International</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://icprsinternational.org</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>https://icprsinternational.org/careers</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="n">
+        <v>5</v>
+      </c>
+      <c r="V88" t="n">
+        <v>5</v>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>The website content for both the main page and careers page only displays verification messages ('Please wait while your request is being verified...'), providing no evidence of what the organisation does or its technology functions.</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>Search: monitoring and evaluation consultancy</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA78"/>
+  <autoFilter ref="A1:AA88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6598,7 +9532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L90"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="2"/>
@@ -9340,8 +12274,2860 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>P044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>C024</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Liquid Intelligent Technologies</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>hr@liquid.tech</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://liquid.tech/careers/</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>This is an HR email address published on the careers page of Liquid Intelligent Technologies. (source: https://liquid.tech/careers/)</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>P045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>C024</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Liquid Intelligent Technologies</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>kenya.jobs@liquid.tech</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://liquid.tech/careers/</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>This is a jobs-specific email address for Kenya published on the careers page. (source: https://liquid.tech/careers/)</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>P046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>C028</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Moringa School</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>careerservices@moringaschool.com</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://moringaschool.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>This is a career services email address published on the contact page. (source: https://moringaschool.com/contact-us/)</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>P047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>C028</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Moringa School</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>contact@moringaschool.com</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://moringaschool.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>This is a general contact email address published on the contact page. (source: https://moringaschool.com/contact-us/)</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>P048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>C043</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Rudder Research and Data Analytics LTD</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://rudderdatanalytics.co.ke/careers</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>This is the dedicated careers portal page published on the organisation's website for job and internship listings. (source: https://rudderdatanalytics.co.ke/careers)</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>P049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>C048</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>bolttech</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://bolttech.io/careers/</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>This is the official careers portal of the organisation, which is the most appropriate route for internship applications. (source: https://bolttech.io/careers/)</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>P050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>C049</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>World Food Programme</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://www.wfp.org/careers</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>This is the official careers portal for the organisation. (source: https://www.wfp.org/careers)</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>P051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>C049</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>World Food Programme</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>abeer.etefa@wfp.org</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://www.wfp.org/media-contacts</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>This is a media contacts email address published on the media contacts page. (source: https://www.wfp.org/media-contacts)</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>P052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>C049</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>World Food Programme</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>azfar.deen@wfp.org</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://www.wfp.org/media-contacts</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>This is a media contacts email address published on the media contacts page. (source: https://www.wfp.org/media-contacts)</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>P053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>C050</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>World Health Organization</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://www.who.int/careers</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>This is the official careers portal published by the World Health Organization. (source: https://www.who.int/careers)</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>P054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>C051</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>World Bank</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://www.worldbank.org/ext/en/jobs</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>This is the official careers portal of the organization, providing direct access to job and internship applications. (source: https://www.worldbank.org/ext/en/jobs)</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>P055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>C051</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>World Bank</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>edingamhoudou@worldbank.org</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://www.worldbank.org/ext/en/contacts</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>This is a personal staff email address published on the general contacts page rather than a dedicated recruitment inbox. (source: https://www.worldbank.org/ext/en/contacts)</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>P056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>C051</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>World Bank</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>lyaro@worldbank.org</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://www.worldbank.org/ext/en/contacts</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>This is a personal staff email address published on the general contacts page rather than a dedicated recruitment inbox. (source: https://www.worldbank.org/ext/en/contacts)</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>P057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>C052</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Kenya Red Cross Society</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://redcross.or.ke/careers/</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>This is the organisation's official careers portal URL for job and internship opportunities. (source: https://redcross.or.ke/careers/)</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>P058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>C053</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Amref Health Africa</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://amref.org/careers/</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>This is the dedicated careers portal page published on the organisation's website. (source: https://amref.org/careers/)</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>P059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>C053</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Amref Health Africa</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>info@amref.org</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://amref.org/</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>This is a general information email address published on the homepage of Amref Health Africa. (source: https://amref.org/)</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>P060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>C054</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>PATH</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://www.path.org/who-we-are/careers/</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>This is the dedicated careers portal published on the organisation's website. (source: https://www.path.org/who-we-are/careers/)</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>P061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>C054</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>PATH</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>info@path.org</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://www.path.org/who-we-are/contact-us/</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>This is a general contact email published on the organisation's contact us page. (source: https://www.path.org/who-we-are/contact-us/)</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>P062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>C055</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Population Services International</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>https://www.psi.org/careers/</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>This route is the official careers portal of the organisation. (source: https://www.psi.org/careers/)</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>P063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>C056</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>CARE International</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>https://www.care.org/careers/</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>This is the organisation's careers portal URL for exploring employment and internship opportunities. (source: https://www.care.org/careers/)</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>P064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>C056</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>CARE International</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>corporateinterest@care.org</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>https://www.care.org/about-us/contact-us/</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>This is a corporate interest email address published on the contact page, which is not intended for student internship requests. (source: https://www.care.org/about-us/contact-us/)</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>P065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>C057</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Oxfam</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>https://www.oxfam.org/en/take-action/jobs</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>This is the organisation's official careers portal published on their website. (source: https://www.oxfam.org/en/take-action/jobs)</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>P066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>C059</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Mercy Corps</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>https://www.prosperglobal.org/careers</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>This is the organisation's careers portal published on their website. (source: https://www.prosperglobal.org/careers)</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>P067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>C062</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Central Bank of Kenya</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>https://www.centralbank.go.ke/cbkcareers/</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>This is the official careers portal URL of the Central Bank of Kenya. (source: https://www.centralbank.go.ke/cbkcareers/)</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>P068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>C062</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Central Bank of Kenya</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>comms@centralbank.go.ke</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>https://www.centralbank.go.ke/</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>This is a general communications email address published on the homepage, which is not dedicated to recruitment or HR. (source: https://www.centralbank.go.ke/)</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>P069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>C065</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>The National Treasury Kenya</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>https://treasury.go.ke/vacancy</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>This is the organisation's official vacancy portal published on their website. (source: https://treasury.go.ke/vacancy)</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>P070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>C065</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>The National Treasury Kenya</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>pstnt@treasury.go.ke</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>https://treasury.go.ke/</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>This is an administrative email address published on the main homepage, not a recruitment or careers route. (source: https://treasury.go.ke/)</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>P071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>C069</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Kenya Power</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>customercare@kplc.co.ke</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>https://kplc.co.ke/contact-us</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>This is a customer care email address published on the contact us page, which is not suitable for handling internship requests. (source: https://kplc.co.ke/contact-us)</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>P072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>C070</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Wasoko</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>https://wasoko.com/careers/</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>This is the official careers portal of the organisation, hosted at https://wasoko.com/careers/. (source: https://wasoko.com/careers/)</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>P073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>C071</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Pezesha</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>https://pezesha.com/careers/</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>This is the careers portal URL published on the organization's website. (source: https://pezesha.com/careers/)</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>P074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>C071</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Pezesha</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>hello@pezesha.com</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>https://pezesha.com/</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>This is a general enquiries email address published on the organization's homepage. (source: https://pezesha.com/)</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>P075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>C072</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>4G Capital</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>https://www.4g-capital.com/workwithus</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>This is the careers portal URL published on the organisation's website. (source: https://www.4g-capital.com/workwithus)</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>P076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>C072</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>4G Capital</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>contact@4g-capital.com</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>https://www.4g-capital.com/</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>This is a general contact address published on the main website. (source: https://www.4g-capital.com/)</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>P077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>C072</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>4G Capital</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>raising.concerns@4g-capital.com</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>https://www.4g-capital.com/</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>This is a specialized concerns address published on the main website, not intended for internship applications. (source: https://www.4g-capital.com/)</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>P078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>C073</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Turaco</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>https://turaco.breezy.hr/</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>This is a dedicated careers portal URL hosted on Breezy.hr for job applications. (source: https://turaco.breezy.hr/)</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>P079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>C073</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Turaco</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>enquiry@turaco.insure</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>https://turaco.insure/contact</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>This email address was published on the contact page of the organisation's website as a general enquiry route. (source: https://turaco.insure/contact)</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>P080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>C074</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Jumia Kenya</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>https://www.jumia.co.ke/mizani-25-miracle-nourishing-hair-oil-125ml-provides-lightweight-hydration-shine-frizz-control-infused-with-coconut-and-jojoba-oil-to-enhance-softness-and-manageability-for-all-hair-types-33638355.html</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>This observed contact is a product page for a hair oil on the e-commerce marketplace and not a recruitment or contact route. (source: https://www.jumia.co.ke/mizani-25-miracle-nourishing-hair-oil-125ml-provides-lightweight-hydration-shine-frizz-control-infused-with-coconut-and-jojoba-oil-to-enhance-softness-and-manageability-for-all-hair-types-33638355.html)</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>P081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>C076</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>https://careers.glovoapp.com/</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>This route is the dedicated careers portal published on Glovo's website for job and internship applications. (source: https://careers.glovoapp.com/)</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>P082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>C017</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>JamboPay</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Searched on 2026-09-15: Pages were read but no email address or careers page was published on them.</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>NONE_FOUND</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>P083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>C045</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>BETA Agriculture Technologies</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Searched on 2026-09-15: Pages were read but no email address or careers page was published on them.</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>NONE_FOUND</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>P084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>C077</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Bolt</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>https://bolt.eu/en/careers/</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>This route is the official careers portal published on Bolt's website. (source: https://bolt.eu/en/careers/)</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>P085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>C078</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ackyshine Monitoring and Evaluation Consultancy</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>https://mobile.ackyshine.com/careers</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>This is the organisation's official careers portal retrieved from their website. (source: https://mobile.ackyshine.com/careers)</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>P086</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>C083</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Third Party Monitoring and Evaluation Limited</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>https://thirdpartymonitoring.com/careers/</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>This is the careers portal page published on the organisation's website for job and internship opportunities. (source: https://thirdpartymonitoring.com/careers/)</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>P087</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>C085</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>MNC Consulting</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>hr@mncconsulting.co.ke</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>https://hr.mncconsulting.co.ke/careers/</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>This is an HR email address published on the careers page of the organisation's website. (source: https://hr.mncconsulting.co.ke/careers/)</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>P088</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>C085</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>MNC Consulting</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Careers / application portal</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Internship/Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>https://hr.mncconsulting.co.ke/careers/</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>This is the dedicated careers portal URL published by the organisation. (source: https://hr.mncconsulting.co.ke/careers/)</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>P089</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>C085</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>MNC Consulting</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>info@mncconsulting.co.ke</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>https://mncconsulting.co.ke/</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>This is a general enquiries email address published on the main website. (source: https://mncconsulting.co.ke/)</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L44"/>
+  <autoFilter ref="A1:L90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11749,7 +17535,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -11822,7 +17608,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -11894,7 +17680,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -11966,7 +17752,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -12039,7 +17825,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -12112,7 +17898,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -12184,7 +17970,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -12256,7 +18042,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -12328,7 +18114,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -12400,7 +18186,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -12472,7 +18258,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -12544,7 +18330,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -12617,7 +18403,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -12690,7 +18476,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -12762,7 +18548,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -12835,7 +18621,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -12907,7 +18693,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -12980,7 +18766,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -13053,7 +18839,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -13126,7 +18912,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">

--- a/data/internship_outreach.xlsx
+++ b/data/internship_outreach.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$AA$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Contacts'!$A$1:$L$90</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Outreach'!$A$1:$T$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Outreach'!$A$1:$T$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Settings'!$A$1:$B$15</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>An international financial institution that provides loans, advice, and research to developing countries to reduce poverty and promote development.</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>The Kenya Red Cross Society is a humanitarian relief organization that works to alleviate human suffering, manage disasters, and provide health and community services.</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Amref Health Africa works with communities and governments to strengthen health systems and advance African-led health solutions.</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>PATH transforms innovative ideas into global health breakthroughs, operating in over 70 countries including Kenya.</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Population Services International is a global network of locally-led organizations focused on transforming health by tackling root causes and delivering healthcare products and services.</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>CARE International is an international humanitarian aid and development organization dedicated to ending poverty and providing emergency support.</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -15138,7 +15138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T51"/>
+  <dimension ref="A1:T57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="3"/>
@@ -15272,7 +15272,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P001</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -15505,7 +15505,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P025</t>
+          <t>P026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -15654,7 +15654,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>DRAFTED</t>
+          <t>SENT</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -15708,9 +15708,19 @@
           <t>2026-09-14</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gmail message id: 1a0a48cb0ce8936a</t>
         </is>
       </c>
     </row>
@@ -16233,7 +16243,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>P016</t>
+          <t>P017</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -16532,7 +16542,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>P025</t>
+          <t>P026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -16609,7 +16619,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>P046</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -16682,7 +16692,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>P028</t>
+          <t>P029</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -16727,7 +16737,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>DRAFTED</t>
+          <t>SENT</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -16735,9 +16745,19 @@
           <t>2026-09-14</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gmail message id: 1a0a48d281f42132</t>
         </is>
       </c>
     </row>
@@ -16836,7 +16856,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>P034</t>
+          <t>P035</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -16881,7 +16901,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>DRAFTED</t>
+          <t>SENT</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -16889,9 +16909,19 @@
           <t>2026-09-14</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gmail message id: 1a0a48da081ed55d</t>
         </is>
       </c>
     </row>
@@ -17341,7 +17371,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>P048</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -17418,7 +17448,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>P046</t>
+          <t>P048</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -17495,7 +17525,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>P047</t>
+          <t>P049</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -17567,7 +17597,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>P048</t>
+          <t>P051</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -17613,7 +17643,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>DRAFTED</t>
+          <t>SENT</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -17621,9 +17651,19 @@
           <t>2026-09-15</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gmail message id: 1a0a48e18f293966</t>
         </is>
       </c>
     </row>
@@ -17640,7 +17680,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>P049</t>
+          <t>P053</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -17712,7 +17752,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>P050</t>
+          <t>P055</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -17757,7 +17797,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>DRAFTED</t>
+          <t>SENT</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -17765,9 +17805,19 @@
           <t>2026-09-15</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gmail message id: 1a0a48e910ff70fe</t>
         </is>
       </c>
     </row>
@@ -17784,7 +17834,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>P051</t>
+          <t>P057</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -17857,7 +17907,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>P052</t>
+          <t>P059</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -17903,7 +17953,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>DRAFTED</t>
+          <t>SENT</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -17911,9 +17961,19 @@
           <t>2026-09-15</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gmail message id: 1a0a4940b8d1ce3b</t>
         </is>
       </c>
     </row>
@@ -17930,7 +17990,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>P054</t>
+          <t>P061</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -17975,7 +18035,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>DRAFTED</t>
+          <t>SENT</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -17983,9 +18043,19 @@
           <t>2026-09-15</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gmail message id: 1a0a4948368bdeba</t>
         </is>
       </c>
     </row>
@@ -18002,7 +18072,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>P056</t>
+          <t>P062</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -18074,7 +18144,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>P057</t>
+          <t>P064</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -18119,7 +18189,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>DRAFTED</t>
+          <t>SENT</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -18127,9 +18197,19 @@
           <t>2026-09-15</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gmail message id: 1a0a494fca1bda15</t>
         </is>
       </c>
     </row>
@@ -18146,7 +18226,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>P059</t>
+          <t>P065</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -18218,7 +18298,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>P060</t>
+          <t>P066</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -18290,7 +18370,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>P061</t>
+          <t>P068</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -18335,7 +18415,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>DRAFTED</t>
+          <t>SENT</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -18343,9 +18423,19 @@
           <t>2026-09-15</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gmail message id: 1a0a4957571902b0</t>
         </is>
       </c>
     </row>
@@ -18362,7 +18452,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>P063</t>
+          <t>P070</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -18408,7 +18498,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>DRAFTED</t>
+          <t>SENT</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -18416,9 +18506,19 @@
           <t>2026-09-15</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gmail message id: 1a0a495ecf76000d</t>
         </is>
       </c>
     </row>
@@ -18435,7 +18535,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>P065</t>
+          <t>P071</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -18481,7 +18581,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>DRAFTED</t>
+          <t>SENT</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -18489,9 +18589,19 @@
           <t>2026-09-15</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gmail message id: 1a0a49a5ce9ea91c</t>
         </is>
       </c>
     </row>
@@ -18508,7 +18618,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>P066</t>
+          <t>P072</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -18580,7 +18690,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>P067</t>
+          <t>P074</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -18626,7 +18736,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>DRAFTED</t>
+          <t>SENT</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -18634,9 +18744,19 @@
           <t>2026-09-15</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gmail message id: 1a0a49ad527e0f24</t>
         </is>
       </c>
     </row>
@@ -18653,7 +18773,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>P069</t>
+          <t>P076</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -18698,7 +18818,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>DRAFTED</t>
+          <t>SENT</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -18706,9 +18826,19 @@
           <t>2026-09-15</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gmail message id: 1a0a49b4c026b921</t>
         </is>
       </c>
     </row>
@@ -18725,7 +18855,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>P072</t>
+          <t>P079</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -18771,7 +18901,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>DRAFTED</t>
+          <t>SENT</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -18779,9 +18909,19 @@
           <t>2026-09-15</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gmail message id: 1a0a49bc444ffadf</t>
         </is>
       </c>
     </row>
@@ -18798,7 +18938,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>P074</t>
+          <t>P081</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -18871,7 +19011,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>P075</t>
+          <t>P084</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -18931,8 +19071,454 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>O051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>C074</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>P080</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Jumia Kenya</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Campaign 2 - Software / Technology Internship</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Industrial attachment enquiry - software and web development</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Dear Jumia Kenya Team,
+I am Monica Wughanga Masae, a BSc Data Science student at the Open University of Kenya, graduating in 2027.
+I am writing to express my interest in an internship or industrial attachment focusing on software and web development, and application support work, given that you operate an online e-commerce marketplace and retail platform involving e-commerce platform development and web and application operations.
+Through my studies and personal work, I have built skills in Python, R, SQL, web development, and software projects, along with data analysis and reporting. I am looking to contribute to your technology operations while gaining practical experience.
+Could you please let me know if you consider students for an industrial attachment or internship placement in these areas, and who the appropriate person to speak with would be if this is outside your remit?
+Thank you for your time.
+Kind regards,
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>O052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>C017</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>P082</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>JamboPay</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Campaign 1 - Data / Analytics Internship</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Internship enquiry - data analysis and reporting, BSc Data Science student</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Dear JamboPay Team,
+I am a student at the Open University of Kenya pursuing a BSc in Data Science, with an expected graduation year of 2027.
+I am reaching out regarding internship and industrial attachment opportunities because of your work providing regulated payment gateway, checkout APIs, and financial transaction infrastructure.
+Through my studies and projects, I have built practical skills in Python, R, SQL, Excel, data analysis, and data visualization using tools like Tableau. I am looking for a placement where I can contribute to data analysis, reporting, and visualization work while learning from your team.
+Could you let me know if you consider interns or industrial attachment students, and who the appropriate person is to speak with regarding these opportunities?
+Thank you for your time.
+Kind regards,
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>O053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>C045</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>P083</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>BETA Agriculture Technologies</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Campaign 1 - Data / Analytics Internship</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Internship enquiry - data analysis, BSc Data Science student</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Dear BETA Agriculture Technologies Team,
+I am a BSc Data Science student at the Open University of Kenya, expecting to graduate in 2027.
+I am writing to enquire about internship or industrial attachment opportunities relating to the digital solutions powered by AI, IoT, satellite monitoring, and precision farming technologies that you provide for farmers, agribusinesses, and financial institutions in East Africa.
+Through my studies and software projects, I have built practical skills in data analysis, reporting, data visualization, Python, R, SQL, and Excel. I am looking for a placement where I can contribute to data analysis and reporting work while learning from your deployment of AI-powered agronomy, satellite monitoring, IoT smart sensors, and data analytics for agriculture.
+Could you please let me know if you would consider an intern or industrial attachment placement, and who I should speak with if you are not the correct contact?
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>O054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>C078</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>P085</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Ackyshine Monitoring and Evaluation Consultancy</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Campaign 1 - Data / Analytics Internship</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Internship enquiry - data analysis and reporting, BSc Data Science student</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Dear Ackyshine Monitoring and Evaluation Consultancy Team,
+I am Monica Wughanga Masae, a BSc Data Science student at the Open University of Kenya graduating in 2027.
+I am writing to enquire about potential internship or industrial attachment opportunities relating to your AI-integrated digital platform, which involves data dashboards, modules, and AI support.
+Through my studies and personal projects, I have built practical skills in Python, R, SQL, and Excel. My strongest area is data analysis, reporting, and visualization, supported by exposure to Tableau, basic statistics, and software projects. I am eager to contribute to your data analysis and reporting tasks while further developing my technical skills.
+Could you please let me know if you would consider an intern or industrial attachment placement for this type of work, or direct me to the right person to speak with if you handle these enquiries elsewhere?
+Thank you for your time.
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>O055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>C083</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>P086</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Third Party Monitoring and Evaluation Limited</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Campaign 1 - Data / Analytics Internship</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Internship enquiry - data analysis, reporting and visualisation</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Dear Third Party Monitoring and Evaluation Limited Team,
+My name is Monica Wughanga Masae, and I am studying BSc Data Science at the Open University of Kenya, with an expected graduation year of 2027.
+I am reaching out because Third Party Monitoring and Evaluation Limited provides project monitoring, evaluation, learning, research, and data analytics services, with a technology function that includes data analytics, data visualizations, M&amp;E systems, automated research tools coding, and cloud data hosting.
+Through my studies, I have built skills in data analysis, reporting, data visualization, Python, R, Excel, SQL, and Tableau exposure. I want to apply these skills to support your data analysis, reporting, and visualisation work while learning practical workflows in an organisation focused on research and data analytics.
+I am writing to ask whether you would consider a student for an internship or industrial attachment placement, and who I should speak with if you accept applications for these roles.
+Thank you for your time.
+Kind regards,
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>DRAFTED</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>O056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>C085</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>P087</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>MNC Consulting</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Campaign 1 - Data / Analytics Internship</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Internship enquiry - data analysis and reporting, BSc Data Science student</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Dear MNC Consulting Team,
+I am Monica Wughanga Masae, a BSc Data Science student at the Open University of Kenya, graduating in 2027. I am writing to enquire about an internship or industrial attachment.
+I am interested in your work in communication services such as USSD and Bulk SMS, as well as digital HR modules including HR Analytics.
+Through my studies and personal projects, I have built skills in Python, R, SQL, Excel, data analysis, reporting, and data visualization. I am looking to contribute to your data analysis, reporting, and visualization work while learning practical operations in a professional setting.
+Could you please let me know if you consider interns or industrial attachment students, and who I should direct my application to if appropriate?
+Thank you for your time.
+Kind regards,
+Monica Wughanga Masae
+BSc Data Science, Open University of Kenya (expected 2027)
+monicawughanga@gmail.com
+LinkedIn: https://www.linkedin.com/in/monica-masae/
+GitHub: https://github.com/M0nicah</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>SENT</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gmail message id: 1a0a4af713ed128b</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T51"/>
+  <autoFilter ref="A1:T57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
